--- a/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="314" documentId="11_10448CB3BBC8A79A89107E47BA0E9DE9642947D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{648E3B9B-1954-40AB-B2C9-A9FDDC2730AE}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="11_10448CB3BBC8A79A89107E47BA0E9DE9642947D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B5FED53-3421-4D20-B272-A355054900EF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -194,9 +197,6 @@
     </r>
   </si>
   <si>
-    <t>Energy (MW added)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Number of HH provided with Solar home lighting systems </t>
   </si>
   <si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
   </si>
   <si>
     <t>Health Services</t>
@@ -704,33 +707,33 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1089,16 +1092,16 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="225">
-      <c r="A2" s="32">
+      <c r="A2" s="34">
         <v>104187</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="34">
         <v>4934228</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -1113,15 +1116,15 @@
       <c r="H2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="33" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="135">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
+      <c r="A3" s="35"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
       <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
@@ -1134,13 +1137,13 @@
       <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="31"/>
+      <c r="I3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="240">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
@@ -1153,7 +1156,7 @@
       <c r="H4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="31"/>
+      <c r="I4" s="33"/>
     </row>
     <row r="5" spans="1:11" ht="120">
       <c r="A5" s="5">
@@ -1243,7 +1246,7 @@
       </c>
       <c r="K7" s="17"/>
     </row>
-    <row r="8" spans="1:11" ht="60">
+    <row r="8" spans="1:11" ht="45.75">
       <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
@@ -1254,10 +1257,10 @@
         <v>1348200</v>
       </c>
       <c r="E8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>15</v>
@@ -1265,11 +1268,11 @@
       <c r="H8" s="5">
         <v>5000</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="15" t="s">
         <v>40</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45">
@@ -1286,7 +1289,7 @@
         <v>29</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>15</v>
@@ -1294,9 +1297,9 @@
       <c r="H9" s="9">
         <v>50000</v>
       </c>
-      <c r="I9" s="30"/>
+      <c r="I9" s="32"/>
       <c r="J9" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60.75">
@@ -1310,10 +1313,10 @@
         <v>753600</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>15</v>
@@ -1321,12 +1324,12 @@
       <c r="H10" s="5">
         <v>100</v>
       </c>
-      <c r="I10" s="30"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K10" s="39" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60.75">
@@ -1340,20 +1343,20 @@
         <v>1906800</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11" s="5">
         <v>168</v>
       </c>
-      <c r="I11" s="30"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="91.5">
@@ -1370,7 +1373,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>15</v>
@@ -1378,12 +1381,12 @@
       <c r="H12" s="5">
         <v>56</v>
       </c>
-      <c r="I12" s="30"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="106.5">
@@ -1400,7 +1403,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>15</v>
@@ -1408,12 +1411,12 @@
       <c r="H13" s="5">
         <v>56</v>
       </c>
-      <c r="I13" s="30"/>
+      <c r="I13" s="32"/>
       <c r="J13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="39" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="90">
@@ -1427,10 +1430,10 @@
         <v>1030400</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>51</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>15</v>
@@ -1438,9 +1441,9 @@
       <c r="H14" s="5">
         <v>100</v>
       </c>
-      <c r="I14" s="30"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="91.5">
@@ -1458,7 +1461,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>15</v>
@@ -1466,12 +1469,12 @@
       <c r="H15" s="13">
         <v>56</v>
       </c>
-      <c r="I15" s="30"/>
+      <c r="I15" s="32"/>
       <c r="J15" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="39" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="60.75">
@@ -1489,7 +1492,7 @@
         <v>25</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>15</v>
@@ -1497,12 +1500,12 @@
       <c r="H16" s="13">
         <v>34</v>
       </c>
-      <c r="I16" s="30"/>
+      <c r="I16" s="32"/>
       <c r="J16" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="76.5">
@@ -1520,7 +1523,7 @@
         <v>25</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>15</v>
@@ -1528,12 +1531,12 @@
       <c r="H17" s="13">
         <v>4</v>
       </c>
-      <c r="I17" s="30"/>
+      <c r="I17" s="32"/>
       <c r="J17" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="39" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="60">
@@ -1541,29 +1544,29 @@
         <v>36</v>
       </c>
       <c r="B18" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D18" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="60">
@@ -1571,29 +1574,29 @@
         <v>36</v>
       </c>
       <c r="B19" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D19" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="28" t="s">
-        <v>38</v>
-      </c>
       <c r="F19" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="60">
@@ -1601,29 +1604,29 @@
         <v>36</v>
       </c>
       <c r="B20" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" s="28" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="60">
@@ -1631,29 +1634,29 @@
         <v>36</v>
       </c>
       <c r="B21" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D21" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" s="28" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="60">
@@ -1661,29 +1664,29 @@
         <v>36</v>
       </c>
       <c r="B22" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D22" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" s="28" t="s">
         <v>58</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I22" s="11"/>
       <c r="J22" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="60">
@@ -1691,29 +1694,29 @@
         <v>36</v>
       </c>
       <c r="B23" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D23" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G23" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I23" s="11"/>
       <c r="J23" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="60">
@@ -1721,29 +1724,29 @@
         <v>36</v>
       </c>
       <c r="B24" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D24" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" s="28" t="s">
         <v>60</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I24" s="11"/>
       <c r="J24" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="60">
@@ -1751,29 +1754,29 @@
         <v>36</v>
       </c>
       <c r="B25" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D25" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E25" s="28" t="s">
         <v>61</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I25" s="11"/>
       <c r="J25" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="60">
@@ -1781,29 +1784,29 @@
         <v>36</v>
       </c>
       <c r="B26" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C26" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D26" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" s="28" t="s">
         <v>62</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I26" s="11"/>
       <c r="J26" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60">
@@ -1811,29 +1814,29 @@
         <v>36</v>
       </c>
       <c r="B27" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D27" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E27" s="28" t="s">
         <v>63</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I27" s="11"/>
       <c r="J27" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="60">
@@ -1841,29 +1844,29 @@
         <v>36</v>
       </c>
       <c r="B28" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D28" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" s="28" t="s">
         <v>64</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="60">
@@ -1871,29 +1874,29 @@
         <v>36</v>
       </c>
       <c r="B29" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="27" t="s">
-        <v>56</v>
-      </c>
       <c r="D29" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E29" s="28" t="s">
         <v>13</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G29" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I29" s="11"/>
       <c r="J29" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="100.5" customHeight="1">
@@ -1952,7 +1955,7 @@
       <c r="I32" s="11"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="30" t="s">
         <v>70</v>
       </c>
       <c r="B33" s="11"/>
@@ -2410,7 +2413,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="36" t="s">
         <v>73</v>
       </c>
       <c r="B2" t="s">
@@ -2421,16 +2424,16 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="34"/>
+      <c r="A3" s="36"/>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="34"/>
+      <c r="A4" s="36"/>
       <c r="B4" t="s">
         <v>29</v>
       </c>
@@ -2439,7 +2442,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="37" t="s">
         <v>77</v>
       </c>
       <c r="B5" t="s">
@@ -2450,7 +2453,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="35"/>
+      <c r="A6" s="37"/>
       <c r="B6" t="s">
         <v>58</v>
       </c>
@@ -2459,7 +2462,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="35"/>
+      <c r="A7" s="37"/>
       <c r="B7" t="s">
         <v>59</v>
       </c>
@@ -2468,7 +2471,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="35"/>
+      <c r="A8" s="37"/>
       <c r="B8" t="s">
         <v>60</v>
       </c>
@@ -2477,7 +2480,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="35"/>
+      <c r="A9" s="37"/>
       <c r="B9" t="s">
         <v>82</v>
       </c>
@@ -2486,7 +2489,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="38" t="s">
         <v>84</v>
       </c>
       <c r="B10" t="s">
@@ -2497,7 +2500,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="36"/>
+      <c r="A11" s="38"/>
       <c r="B11" t="s">
         <v>61</v>
       </c>
@@ -2506,7 +2509,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="39" t="s">
         <v>88</v>
       </c>
       <c r="B12" t="s">
@@ -2517,7 +2520,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="37"/>
+      <c r="A13" s="39"/>
       <c r="B13" t="s">
         <v>63</v>
       </c>
@@ -2526,7 +2529,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="37"/>
+      <c r="A14" s="39"/>
       <c r="B14" t="s">
         <v>64</v>
       </c>
@@ -2568,8 +2571,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd739a91710fed73edeed3c312976475">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="829e6ebd84bdd7e43dc34d34aecb984e" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -2593,6 +2605,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2668,6 +2681,11 @@
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fb9e4d32-074f-4c04-81ef-e811753dfd59" elementFormDefault="qualified">
@@ -2810,15 +2828,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2883,11 +2892,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{356C69F5-D64B-47C1-A11D-A8E47D3E386F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7AE853E-4F37-4A3C-B15C-49DE17FB657C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7AE853E-4F37-4A3C-B15C-49DE17FB657C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83981D53-9EA2-4F8A-A632-D9F3E2E44328}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/SEH/Energy-Moonshot-Tracker/01_Input/00_CO Validation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDB382D-5162-0D4B-A9D6-F478C37769CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="11_10448CB3BBC8A79A89107E47BA0E9DE9642947D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6606264-F8AF-4CC0-91FA-4D33866BF24B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="740" windowWidth="20740" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (4)" sheetId="5" r:id="rId1"/>
@@ -247,7 +247,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">UNDP-SPM Partnership for rural electrification
 </t>
@@ -257,7 +256,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>(Concept developed subject to resource mobilization)</t>
     </r>
@@ -441,7 +439,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve">3 villages in Shan state were supported with 1 solar pumping system and 2 solar bubble dryers. 
 </t>
@@ -451,7 +448,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>Solar pumping - 15 HH
 Solar dryers - 30 HH in total (two villages)</t>
@@ -461,7 +457,6 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -643,7 +638,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,7 +650,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -722,9 +716,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -745,14 +748,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -973,7 +974,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -987,16 +988,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1005,27 +1006,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1038,7 +1039,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1078,10 +1079,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1122,6 +1123,33 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1130,33 +1158,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1493,27 +1494,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{778F1655-3D46-4BD6-BB17-1CD9D47FFDE3}">
   <dimension ref="A1:W69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="48.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="13" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="9.1640625" style="2"/>
-    <col min="19" max="19" width="13.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="2"/>
+    <col min="12" max="12" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="9.140625" style="2"/>
+    <col min="19" max="19" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +1579,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="139.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="139.5" customHeight="1">
       <c r="A2" s="58">
         <v>104187</v>
       </c>
@@ -1623,7 +1624,7 @@
       <c r="T2" s="66"/>
       <c r="U2" s="68"/>
     </row>
-    <row r="3" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="60.75">
       <c r="E3" s="71" t="s">
         <v>30</v>
       </c>
@@ -1654,7 +1655,7 @@
       <c r="T3" s="66"/>
       <c r="U3" s="68"/>
     </row>
-    <row r="4" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="76.5">
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
@@ -1685,7 +1686,7 @@
       <c r="T4" s="66"/>
       <c r="U4" s="68"/>
     </row>
-    <row r="5" spans="1:23" ht="80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="91.5">
       <c r="A5" s="2">
         <v>111777</v>
       </c>
@@ -1730,7 +1731,7 @@
       <c r="T5" s="66"/>
       <c r="U5" s="68"/>
     </row>
-    <row r="6" spans="1:23" ht="96" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="106.5">
       <c r="C6" s="3"/>
       <c r="D6" s="5"/>
       <c r="E6" s="2" t="s">
@@ -1763,7 +1764,7 @@
       <c r="T6" s="66"/>
       <c r="U6" s="68"/>
     </row>
-    <row r="7" spans="1:23" ht="224" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="244.5">
       <c r="C7" s="3"/>
       <c r="D7" s="5"/>
       <c r="E7" s="2" t="s">
@@ -1797,7 +1798,7 @@
       <c r="U7" s="68"/>
       <c r="W7" s="14"/>
     </row>
-    <row r="8" spans="1:23" ht="48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="45.75">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
@@ -1819,7 +1820,7 @@
       <c r="H8" s="2">
         <v>5000</v>
       </c>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="75" t="s">
         <v>54</v>
       </c>
       <c r="J8" s="12" t="s">
@@ -1840,7 +1841,7 @@
       <c r="T8" s="66"/>
       <c r="U8" s="68"/>
     </row>
-    <row r="9" spans="1:23" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="45.75">
       <c r="B9" s="7"/>
       <c r="D9" s="6">
         <v>1624000</v>
@@ -1857,7 +1858,7 @@
       <c r="H9" s="6">
         <v>50000</v>
       </c>
-      <c r="I9" s="78"/>
+      <c r="I9" s="75"/>
       <c r="J9" s="72"/>
       <c r="L9" s="65" t="s">
         <v>27</v>
@@ -1872,7 +1873,7 @@
       <c r="T9" s="66"/>
       <c r="U9" s="68"/>
     </row>
-    <row r="10" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="76.5">
       <c r="B10" s="7"/>
       <c r="D10" s="6">
         <v>753600</v>
@@ -1889,7 +1890,7 @@
       <c r="H10" s="12">
         <v>100</v>
       </c>
-      <c r="I10" s="78"/>
+      <c r="I10" s="75"/>
       <c r="J10" s="72"/>
       <c r="L10" s="65" t="s">
         <v>27</v>
@@ -1907,7 +1908,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="76.5">
       <c r="B11" s="7"/>
       <c r="D11" s="6">
         <v>1906800</v>
@@ -1922,7 +1923,7 @@
       <c r="H11" s="12">
         <v>168</v>
       </c>
-      <c r="I11" s="78"/>
+      <c r="I11" s="75"/>
       <c r="J11" s="72"/>
       <c r="L11" s="65" t="s">
         <v>27</v>
@@ -1940,7 +1941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="96" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="91.5">
       <c r="B12" s="7"/>
       <c r="D12" s="6">
         <v>682360</v>
@@ -1957,7 +1958,7 @@
       <c r="H12" s="12">
         <v>56</v>
       </c>
-      <c r="I12" s="78"/>
+      <c r="I12" s="75"/>
       <c r="J12" s="72"/>
       <c r="L12" s="65" t="s">
         <v>27</v>
@@ -1975,7 +1976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="96" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="106.5">
       <c r="B13" s="7"/>
       <c r="D13" s="6">
         <v>529200</v>
@@ -1992,7 +1993,7 @@
       <c r="H13" s="12">
         <v>56</v>
       </c>
-      <c r="I13" s="78"/>
+      <c r="I13" s="75"/>
       <c r="J13" s="72"/>
       <c r="L13" s="65" t="s">
         <v>27</v>
@@ -2010,7 +2011,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="80" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="91.5">
       <c r="B14" s="7"/>
       <c r="D14" s="6">
         <v>1030400</v>
@@ -2027,7 +2028,7 @@
       <c r="H14" s="12">
         <v>100</v>
       </c>
-      <c r="I14" s="78"/>
+      <c r="I14" s="75"/>
       <c r="J14" s="72"/>
       <c r="L14" s="65" t="s">
         <v>27</v>
@@ -2042,7 +2043,7 @@
       <c r="T14" s="66"/>
       <c r="U14" s="68"/>
     </row>
-    <row r="15" spans="1:23" ht="96" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="91.5">
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11">
@@ -2060,7 +2061,7 @@
       <c r="H15" s="74">
         <v>56</v>
       </c>
-      <c r="I15" s="78"/>
+      <c r="I15" s="75"/>
       <c r="J15" s="72"/>
       <c r="L15" s="65" t="s">
         <v>27</v>
@@ -2078,7 +2079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="76.5">
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11">
@@ -2096,7 +2097,7 @@
       <c r="H16" s="74">
         <v>34</v>
       </c>
-      <c r="I16" s="78"/>
+      <c r="I16" s="75"/>
       <c r="J16" s="72"/>
       <c r="L16" s="65" t="s">
         <v>27</v>
@@ -2114,7 +2115,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="76.5">
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11">
@@ -2132,7 +2133,7 @@
       <c r="H17" s="10">
         <v>4</v>
       </c>
-      <c r="I17" s="78"/>
+      <c r="I17" s="75"/>
       <c r="J17" s="72"/>
       <c r="L17" s="65" t="s">
         <v>27</v>
@@ -2150,7 +2151,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="48" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="60.75">
       <c r="B18" s="24" t="s">
         <v>69</v>
       </c>
@@ -2187,7 +2188,7 @@
       <c r="T18" s="66"/>
       <c r="U18" s="68"/>
     </row>
-    <row r="19" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23">
       <c r="A19" s="8"/>
       <c r="B19" s="24"/>
       <c r="C19" s="24" t="s">
@@ -2224,7 +2225,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23">
       <c r="A20" s="8"/>
       <c r="B20" s="24"/>
       <c r="C20" s="24" t="s">
@@ -2258,7 +2259,7 @@
       <c r="T20" s="66"/>
       <c r="U20" s="68"/>
     </row>
-    <row r="21" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23">
       <c r="A21" s="8"/>
       <c r="B21" s="24"/>
       <c r="C21" s="24" t="s">
@@ -2292,7 +2293,7 @@
       <c r="T21" s="66"/>
       <c r="U21" s="68"/>
     </row>
-    <row r="22" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23">
       <c r="A22" s="26"/>
       <c r="B22" s="24"/>
       <c r="C22" s="24" t="s">
@@ -2326,7 +2327,7 @@
       <c r="T22" s="66"/>
       <c r="U22" s="68"/>
     </row>
-    <row r="23" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23">
       <c r="A23" s="26"/>
       <c r="B23" s="24"/>
       <c r="C23" s="24" t="s">
@@ -2360,7 +2361,7 @@
       <c r="T23" s="66"/>
       <c r="U23" s="68"/>
     </row>
-    <row r="24" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23">
       <c r="A24" s="26"/>
       <c r="B24" s="24"/>
       <c r="C24" s="24" t="s">
@@ -2394,7 +2395,7 @@
       <c r="T24" s="66"/>
       <c r="U24" s="68"/>
     </row>
-    <row r="25" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23">
       <c r="A25" s="26"/>
       <c r="B25" s="24"/>
       <c r="C25" s="24" t="s">
@@ -2428,7 +2429,7 @@
       <c r="T25" s="66"/>
       <c r="U25" s="68"/>
     </row>
-    <row r="26" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23">
       <c r="A26" s="26"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24" t="s">
@@ -2462,7 +2463,7 @@
       <c r="T26" s="66"/>
       <c r="U26" s="68"/>
     </row>
-    <row r="27" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23">
       <c r="A27" s="26"/>
       <c r="B27" s="24"/>
       <c r="C27" s="24" t="s">
@@ -2496,7 +2497,7 @@
       <c r="T27" s="66"/>
       <c r="U27" s="68"/>
     </row>
-    <row r="28" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23">
       <c r="A28" s="26"/>
       <c r="B28" s="24"/>
       <c r="C28" s="24" t="s">
@@ -2530,7 +2531,7 @@
       <c r="T28" s="66"/>
       <c r="U28" s="68"/>
     </row>
-    <row r="29" spans="1:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23">
       <c r="A29" s="26"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
@@ -2564,7 +2565,7 @@
       <c r="T29" s="66"/>
       <c r="U29" s="68"/>
     </row>
-    <row r="30" spans="1:23" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="100.5" customHeight="1">
       <c r="A30" s="17">
         <v>112026</v>
       </c>
@@ -2611,7 +2612,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -2622,7 +2623,7 @@
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -2633,7 +2634,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -2642,7 +2643,7 @@
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -2653,7 +2654,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -2664,7 +2665,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2675,7 +2676,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -2686,7 +2687,7 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -2697,7 +2698,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2708,7 +2709,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -2719,7 +2720,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -2730,7 +2731,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2741,7 +2742,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -2752,7 +2753,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -2763,7 +2764,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -2774,7 +2775,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -2785,7 +2786,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -2796,7 +2797,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -2807,7 +2808,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -2818,7 +2819,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -2829,7 +2830,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -2840,7 +2841,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -2851,7 +2852,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -2862,7 +2863,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -2873,7 +2874,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -2884,7 +2885,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -2895,7 +2896,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -2906,7 +2907,7 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -2917,7 +2918,7 @@
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -2928,7 +2929,7 @@
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -2939,7 +2940,7 @@
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -2950,7 +2951,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -2961,7 +2962,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -2972,7 +2973,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -2983,7 +2984,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -2994,7 +2995,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -3005,7 +3006,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -3016,7 +3017,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -3027,7 +3028,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -3096,26 +3097,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BDDD6AD-0157-4AD0-8432-5BC784E7D4DE}">
   <dimension ref="A1:O69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="48.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="13" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="31.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" style="2"/>
-    <col min="15" max="15" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1640625" style="2"/>
+    <col min="12" max="12" width="14.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="2"/>
+    <col min="15" max="15" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="75">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -3156,17 +3157,17 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="208" x14ac:dyDescent="0.2">
-      <c r="A2" s="80">
+    <row r="2" spans="1:15" ht="225">
+      <c r="A2" s="77">
         <v>104187</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="80">
+      <c r="D2" s="77">
         <v>4934228</v>
       </c>
       <c r="E2" s="35" t="s">
@@ -3181,7 +3182,7 @@
       <c r="H2" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="78" t="s">
         <v>90</v>
       </c>
       <c r="J2" s="36"/>
@@ -3192,11 +3193,11 @@
       </c>
       <c r="O2" s="29"/>
     </row>
-    <row r="3" spans="1:15" ht="112" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+    <row r="3" spans="1:15" ht="135">
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="36" t="s">
         <v>19</v>
       </c>
@@ -3209,17 +3210,17 @@
       <c r="H3" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="81"/>
+      <c r="I3" s="78"/>
       <c r="J3" s="36"/>
       <c r="K3" s="36"/>
       <c r="L3" s="34"/>
       <c r="M3" s="34"/>
     </row>
-    <row r="4" spans="1:15" ht="192" x14ac:dyDescent="0.2">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
+    <row r="4" spans="1:15" ht="240">
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
       <c r="E4" s="36" t="s">
         <v>92</v>
       </c>
@@ -3232,13 +3233,13 @@
       <c r="H4" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="81"/>
+      <c r="I4" s="78"/>
       <c r="J4" s="36"/>
       <c r="K4" s="36"/>
       <c r="L4" s="34"/>
       <c r="M4" s="34"/>
     </row>
-    <row r="5" spans="1:15" ht="128" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="150">
       <c r="A5" s="36">
         <v>111777</v>
       </c>
@@ -3276,7 +3277,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="192" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="225">
       <c r="A6" s="36">
         <v>111777</v>
       </c>
@@ -3314,7 +3315,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="240" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="255">
       <c r="A7" s="36"/>
       <c r="B7" s="36"/>
       <c r="C7" s="37"/>
@@ -3339,7 +3340,7 @@
       <c r="L7" s="34"/>
       <c r="M7" s="34"/>
     </row>
-    <row r="8" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="60">
       <c r="A8" s="54" t="s">
         <v>51</v>
       </c>
@@ -3362,7 +3363,7 @@
       <c r="H8" s="36">
         <v>5000</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I8" s="76" t="s">
         <v>54</v>
       </c>
       <c r="J8" s="44" t="s">
@@ -3377,7 +3378,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="45">
       <c r="A9" s="36"/>
       <c r="B9" s="42"/>
       <c r="C9" s="36"/>
@@ -3396,7 +3397,7 @@
       <c r="H9" s="43">
         <v>50000</v>
       </c>
-      <c r="I9" s="79"/>
+      <c r="I9" s="76"/>
       <c r="J9" s="44" t="s">
         <v>55</v>
       </c>
@@ -3409,7 +3410,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="60">
       <c r="A10" s="36"/>
       <c r="B10" s="42"/>
       <c r="C10" s="36"/>
@@ -3428,7 +3429,7 @@
       <c r="H10" s="36">
         <v>100</v>
       </c>
-      <c r="I10" s="79"/>
+      <c r="I10" s="76"/>
       <c r="J10" s="44" t="s">
         <v>55</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="60">
       <c r="A11" s="36"/>
       <c r="B11" s="42"/>
       <c r="C11" s="36"/>
@@ -3460,7 +3461,7 @@
       <c r="H11" s="36">
         <v>168</v>
       </c>
-      <c r="I11" s="79"/>
+      <c r="I11" s="76"/>
       <c r="J11" s="44" t="s">
         <v>55</v>
       </c>
@@ -3475,7 +3476,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="90">
       <c r="A12" s="36"/>
       <c r="B12" s="42"/>
       <c r="C12" s="36"/>
@@ -3494,7 +3495,7 @@
       <c r="H12" s="36">
         <v>56</v>
       </c>
-      <c r="I12" s="79"/>
+      <c r="I12" s="76"/>
       <c r="J12" s="44" t="s">
         <v>55</v>
       </c>
@@ -3509,7 +3510,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="135">
       <c r="A13" s="36"/>
       <c r="B13" s="42"/>
       <c r="C13" s="36"/>
@@ -3528,7 +3529,7 @@
       <c r="H13" s="36">
         <v>56</v>
       </c>
-      <c r="I13" s="79"/>
+      <c r="I13" s="76"/>
       <c r="J13" s="44" t="s">
         <v>55</v>
       </c>
@@ -3543,7 +3544,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="90">
       <c r="A14" s="36"/>
       <c r="B14" s="42"/>
       <c r="C14" s="36"/>
@@ -3562,7 +3563,7 @@
       <c r="H14" s="36">
         <v>100</v>
       </c>
-      <c r="I14" s="79"/>
+      <c r="I14" s="76"/>
       <c r="J14" s="44" t="s">
         <v>55</v>
       </c>
@@ -3575,7 +3576,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="90">
       <c r="A15" s="36"/>
       <c r="B15" s="42"/>
       <c r="C15" s="36"/>
@@ -3594,7 +3595,7 @@
       <c r="H15" s="36">
         <v>56</v>
       </c>
-      <c r="I15" s="79"/>
+      <c r="I15" s="76"/>
       <c r="J15" s="44" t="s">
         <v>55</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="60">
       <c r="A16" s="36"/>
       <c r="B16" s="42"/>
       <c r="C16" s="36"/>
@@ -3628,7 +3629,7 @@
       <c r="H16" s="36">
         <v>34</v>
       </c>
-      <c r="I16" s="79"/>
+      <c r="I16" s="76"/>
       <c r="J16" s="44" t="s">
         <v>55</v>
       </c>
@@ -3643,7 +3644,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="75">
       <c r="A17" s="36"/>
       <c r="B17" s="42"/>
       <c r="C17" s="36"/>
@@ -3662,7 +3663,7 @@
       <c r="H17" s="36">
         <v>4</v>
       </c>
-      <c r="I17" s="79"/>
+      <c r="I17" s="76"/>
       <c r="J17" s="44" t="s">
         <v>55</v>
       </c>
@@ -3677,7 +3678,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="60">
       <c r="A18" s="54" t="s">
         <v>51</v>
       </c>
@@ -3710,7 +3711,7 @@
       <c r="L18" s="34"/>
       <c r="M18" s="34"/>
     </row>
-    <row r="19" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13">
       <c r="A19" s="47"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48" t="s">
@@ -3739,7 +3740,7 @@
       <c r="L19" s="34"/>
       <c r="M19" s="34"/>
     </row>
-    <row r="20" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13">
       <c r="A20" s="47"/>
       <c r="B20" s="48"/>
       <c r="C20" s="48" t="s">
@@ -3768,7 +3769,7 @@
       <c r="L20" s="34"/>
       <c r="M20" s="34"/>
     </row>
-    <row r="21" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13">
       <c r="A21" s="47"/>
       <c r="B21" s="48"/>
       <c r="C21" s="48" t="s">
@@ -3797,7 +3798,7 @@
       <c r="L21" s="34"/>
       <c r="M21" s="34"/>
     </row>
-    <row r="22" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13">
       <c r="A22" s="50"/>
       <c r="B22" s="48"/>
       <c r="C22" s="48" t="s">
@@ -3826,7 +3827,7 @@
       <c r="L22" s="34"/>
       <c r="M22" s="34"/>
     </row>
-    <row r="23" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13">
       <c r="A23" s="50"/>
       <c r="B23" s="48"/>
       <c r="C23" s="48" t="s">
@@ -3855,7 +3856,7 @@
       <c r="L23" s="34"/>
       <c r="M23" s="34"/>
     </row>
-    <row r="24" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13">
       <c r="A24" s="50"/>
       <c r="B24" s="48"/>
       <c r="C24" s="48" t="s">
@@ -3884,7 +3885,7 @@
       <c r="L24" s="34"/>
       <c r="M24" s="34"/>
     </row>
-    <row r="25" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13">
       <c r="A25" s="50"/>
       <c r="B25" s="48"/>
       <c r="C25" s="48" t="s">
@@ -3913,7 +3914,7 @@
       <c r="L25" s="34"/>
       <c r="M25" s="34"/>
     </row>
-    <row r="26" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13">
       <c r="A26" s="50"/>
       <c r="B26" s="48"/>
       <c r="C26" s="48" t="s">
@@ -3942,7 +3943,7 @@
       <c r="L26" s="34"/>
       <c r="M26" s="34"/>
     </row>
-    <row r="27" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13">
       <c r="A27" s="50"/>
       <c r="B27" s="48"/>
       <c r="C27" s="48" t="s">
@@ -3971,7 +3972,7 @@
       <c r="L27" s="34"/>
       <c r="M27" s="34"/>
     </row>
-    <row r="28" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13">
       <c r="A28" s="50"/>
       <c r="B28" s="48"/>
       <c r="C28" s="48" t="s">
@@ -4000,7 +4001,7 @@
       <c r="L28" s="34"/>
       <c r="M28" s="34"/>
     </row>
-    <row r="29" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13">
       <c r="A29" s="50"/>
       <c r="B29" s="48"/>
       <c r="C29" s="48" t="s">
@@ -4029,7 +4030,7 @@
       <c r="L29" s="34"/>
       <c r="M29" s="34"/>
     </row>
-    <row r="30" spans="1:13" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="100.5" customHeight="1">
       <c r="A30" s="51">
         <v>112026</v>
       </c>
@@ -4069,7 +4070,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -4080,7 +4081,7 @@
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -4091,7 +4092,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" s="27" t="s">
         <v>72</v>
       </c>
@@ -4103,7 +4104,7 @@
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -4114,7 +4115,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -4125,7 +4126,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -4136,7 +4137,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -4147,7 +4148,7 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -4158,7 +4159,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -4169,7 +4170,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -4180,7 +4181,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -4191,7 +4192,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -4202,7 +4203,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -4213,7 +4214,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -4224,7 +4225,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -4235,7 +4236,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -4246,7 +4247,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -4257,7 +4258,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -4268,7 +4269,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -4279,7 +4280,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -4290,7 +4291,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -4301,7 +4302,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -4312,7 +4313,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -4323,7 +4324,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -4334,7 +4335,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -4345,7 +4346,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -4356,7 +4357,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -4367,7 +4368,7 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -4378,7 +4379,7 @@
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -4389,7 +4390,7 @@
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -4400,7 +4401,7 @@
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -4411,7 +4412,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -4422,7 +4423,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -4433,7 +4434,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -4444,7 +4445,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -4455,7 +4456,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -4466,7 +4467,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -4477,7 +4478,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -4488,7 +4489,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -4532,26 +4533,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4CD46A-09BF-4129-814A-2126A829AC67}">
   <dimension ref="A1:O69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="48.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="13" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="31.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" style="2"/>
-    <col min="15" max="15" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1640625" style="2"/>
+    <col min="12" max="12" width="14.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" style="2"/>
+    <col min="15" max="15" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4592,17 +4593,17 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="208" x14ac:dyDescent="0.2">
-      <c r="A2" s="82">
+    <row r="2" spans="1:15" ht="225">
+      <c r="A2" s="79">
         <v>104187</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="82">
+      <c r="D2" s="79">
         <v>4934228</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -4617,7 +4618,7 @@
       <c r="H2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="81" t="s">
         <v>90</v>
       </c>
       <c r="L2" s="30"/>
@@ -4626,11 +4627,11 @@
       </c>
       <c r="O2" s="29"/>
     </row>
-    <row r="3" spans="1:15" ht="112" x14ac:dyDescent="0.2">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+    <row r="3" spans="1:15" ht="135">
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
       <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
@@ -4643,15 +4644,15 @@
       <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="84"/>
+      <c r="I3" s="81"/>
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="4" spans="1:15" ht="192" x14ac:dyDescent="0.2">
-      <c r="A4" s="83"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
+    <row r="4" spans="1:15" ht="240">
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
       <c r="E4" s="2" t="s">
         <v>92</v>
       </c>
@@ -4664,11 +4665,11 @@
       <c r="H4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="84"/>
+      <c r="I4" s="81"/>
       <c r="L4" s="30"/>
       <c r="M4" s="30"/>
     </row>
-    <row r="5" spans="1:15" ht="128" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="150">
       <c r="A5" s="2">
         <v>111777</v>
       </c>
@@ -4704,7 +4705,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="192" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="225">
       <c r="A6" s="2">
         <v>111777</v>
       </c>
@@ -4740,7 +4741,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="240" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="255">
       <c r="C7" s="3"/>
       <c r="D7" s="5"/>
       <c r="E7" s="2" t="s">
@@ -4762,7 +4763,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="30"/>
     </row>
-    <row r="8" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="60">
       <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
@@ -4784,7 +4785,7 @@
       <c r="H8" s="2">
         <v>5000</v>
       </c>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="75" t="s">
         <v>54</v>
       </c>
       <c r="J8" s="12" t="s">
@@ -4798,7 +4799,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="45">
       <c r="A9" s="2" t="s">
         <v>114</v>
       </c>
@@ -4820,7 +4821,7 @@
       <c r="H9" s="6">
         <v>50000</v>
       </c>
-      <c r="I9" s="78"/>
+      <c r="I9" s="75"/>
       <c r="J9" s="12" t="s">
         <v>55</v>
       </c>
@@ -4832,7 +4833,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="60">
       <c r="A10" s="2" t="s">
         <v>114</v>
       </c>
@@ -4854,7 +4855,7 @@
       <c r="H10" s="2">
         <v>100</v>
       </c>
-      <c r="I10" s="78"/>
+      <c r="I10" s="75"/>
       <c r="J10" s="12" t="s">
         <v>55</v>
       </c>
@@ -4869,7 +4870,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="60">
       <c r="A11" s="2" t="s">
         <v>114</v>
       </c>
@@ -4888,7 +4889,7 @@
       <c r="H11" s="2">
         <v>168</v>
       </c>
-      <c r="I11" s="78"/>
+      <c r="I11" s="75"/>
       <c r="J11" s="12" t="s">
         <v>55</v>
       </c>
@@ -4903,7 +4904,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="90">
       <c r="A12" s="2" t="s">
         <v>114</v>
       </c>
@@ -4925,7 +4926,7 @@
       <c r="H12" s="2">
         <v>56</v>
       </c>
-      <c r="I12" s="78"/>
+      <c r="I12" s="75"/>
       <c r="J12" s="12" t="s">
         <v>55</v>
       </c>
@@ -4940,7 +4941,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="135">
       <c r="A13" s="2" t="s">
         <v>114</v>
       </c>
@@ -4962,7 +4963,7 @@
       <c r="H13" s="2">
         <v>56</v>
       </c>
-      <c r="I13" s="78"/>
+      <c r="I13" s="75"/>
       <c r="J13" s="12" t="s">
         <v>55</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="80" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="90">
       <c r="A14" s="2" t="s">
         <v>114</v>
       </c>
@@ -4999,7 +5000,7 @@
       <c r="H14" s="2">
         <v>100</v>
       </c>
-      <c r="I14" s="78"/>
+      <c r="I14" s="75"/>
       <c r="J14" s="12" t="s">
         <v>55</v>
       </c>
@@ -5011,7 +5012,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="96" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="90">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
@@ -5034,7 +5035,7 @@
       <c r="H15" s="10">
         <v>56</v>
       </c>
-      <c r="I15" s="78"/>
+      <c r="I15" s="75"/>
       <c r="J15" s="12" t="s">
         <v>55</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="64" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="60">
       <c r="A16" s="2" t="s">
         <v>114</v>
       </c>
@@ -5072,7 +5073,7 @@
       <c r="H16" s="10">
         <v>34</v>
       </c>
-      <c r="I16" s="78"/>
+      <c r="I16" s="75"/>
       <c r="J16" s="12" t="s">
         <v>55</v>
       </c>
@@ -5087,7 +5088,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="75">
       <c r="A17" s="2" t="s">
         <v>114</v>
       </c>
@@ -5110,7 +5111,7 @@
       <c r="H17" s="10">
         <v>4</v>
       </c>
-      <c r="I17" s="78"/>
+      <c r="I17" s="75"/>
       <c r="J17" s="12" t="s">
         <v>55</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="60">
       <c r="A18" s="8" t="s">
         <v>114</v>
       </c>
@@ -5157,7 +5158,7 @@
       <c r="L18" s="30"/>
       <c r="M18" s="30"/>
     </row>
-    <row r="19" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="60">
       <c r="A19" s="8" t="s">
         <v>114</v>
       </c>
@@ -5189,7 +5190,7 @@
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
     </row>
-    <row r="20" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="60">
       <c r="A20" s="8" t="s">
         <v>114</v>
       </c>
@@ -5221,7 +5222,7 @@
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
     </row>
-    <row r="21" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" ht="60">
       <c r="A21" s="8" t="s">
         <v>114</v>
       </c>
@@ -5253,7 +5254,7 @@
       <c r="L21" s="30"/>
       <c r="M21" s="30"/>
     </row>
-    <row r="22" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="60">
       <c r="A22" s="26" t="s">
         <v>114</v>
       </c>
@@ -5285,7 +5286,7 @@
       <c r="L22" s="30"/>
       <c r="M22" s="30"/>
     </row>
-    <row r="23" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="60">
       <c r="A23" s="26" t="s">
         <v>114</v>
       </c>
@@ -5317,7 +5318,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="30"/>
     </row>
-    <row r="24" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="60">
       <c r="A24" s="26" t="s">
         <v>114</v>
       </c>
@@ -5349,7 +5350,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="30"/>
     </row>
-    <row r="25" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="60">
       <c r="A25" s="26" t="s">
         <v>114</v>
       </c>
@@ -5381,7 +5382,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="30"/>
     </row>
-    <row r="26" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" ht="60">
       <c r="A26" s="26" t="s">
         <v>114</v>
       </c>
@@ -5413,7 +5414,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="30"/>
     </row>
-    <row r="27" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" ht="60">
       <c r="A27" s="26" t="s">
         <v>114</v>
       </c>
@@ -5445,7 +5446,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="30"/>
     </row>
-    <row r="28" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="60">
       <c r="A28" s="26" t="s">
         <v>114</v>
       </c>
@@ -5477,7 +5478,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="30"/>
     </row>
-    <row r="29" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="60">
       <c r="A29" s="26" t="s">
         <v>114</v>
       </c>
@@ -5509,7 +5510,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="30"/>
     </row>
-    <row r="30" spans="1:13" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" ht="100.5" customHeight="1">
       <c r="A30" s="17">
         <v>112026</v>
       </c>
@@ -5549,7 +5550,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -5560,7 +5561,7 @@
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -5571,7 +5572,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" s="27" t="s">
         <v>72</v>
       </c>
@@ -5583,7 +5584,7 @@
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -5594,7 +5595,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -5605,7 +5606,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -5616,7 +5617,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -5627,7 +5628,7 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -5638,7 +5639,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -5649,7 +5650,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -5660,7 +5661,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -5671,7 +5672,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -5682,7 +5683,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -5693,7 +5694,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -5704,7 +5705,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -5715,7 +5716,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -5726,7 +5727,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -5737,7 +5738,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -5748,7 +5749,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -5759,7 +5760,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -5770,7 +5771,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -5781,7 +5782,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -5792,7 +5793,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -5803,7 +5804,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -5814,7 +5815,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -5825,7 +5826,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -5836,7 +5837,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -5847,7 +5848,7 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -5858,7 +5859,7 @@
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -5869,7 +5870,7 @@
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -5880,7 +5881,7 @@
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -5891,7 +5892,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -5902,7 +5903,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -5913,7 +5914,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -5924,7 +5925,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -5935,7 +5936,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -5946,7 +5947,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -5957,7 +5958,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -5968,7 +5969,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -6012,24 +6013,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="48.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="32.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="23.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="32.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="13" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.5" style="2" customWidth="1"/>
-    <col min="13" max="13" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1640625" style="2"/>
+    <col min="12" max="12" width="19.5703125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="30.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6067,17 +6068,17 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="208" x14ac:dyDescent="0.2">
-      <c r="A2" s="82">
+    <row r="2" spans="1:13" ht="213">
+      <c r="A2" s="79">
         <v>104187</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="82">
+      <c r="D2" s="79">
         <v>4934228</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -6092,7 +6093,7 @@
       <c r="H2" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="81" t="s">
         <v>90</v>
       </c>
       <c r="L2" s="28" t="s">
@@ -6100,11 +6101,11 @@
       </c>
       <c r="M2" s="29"/>
     </row>
-    <row r="3" spans="1:13" ht="112" x14ac:dyDescent="0.2">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
+    <row r="3" spans="1:13" ht="135">
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
       <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
@@ -6117,13 +6118,13 @@
       <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="84"/>
-    </row>
-    <row r="4" spans="1:13" ht="192" x14ac:dyDescent="0.2">
-      <c r="A4" s="83"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
+      <c r="I3" s="81"/>
+    </row>
+    <row r="4" spans="1:13" ht="240">
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
       <c r="E4" s="2" t="s">
         <v>92</v>
       </c>
@@ -6136,9 +6137,9 @@
       <c r="H4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="84"/>
-    </row>
-    <row r="5" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+      <c r="I4" s="81"/>
+    </row>
+    <row r="5" spans="1:13" ht="120">
       <c r="A5" s="2">
         <v>111777</v>
       </c>
@@ -6167,7 +6168,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="121.5">
       <c r="C6" s="3"/>
       <c r="D6" s="5"/>
       <c r="E6" s="2" t="s">
@@ -6186,7 +6187,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="240" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="255">
       <c r="C7" s="3"/>
       <c r="D7" s="5"/>
       <c r="E7" s="2" t="s">
@@ -6206,7 +6207,7 @@
       </c>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" spans="1:13" ht="112" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="121.5">
       <c r="A8" s="2" t="s">
         <v>114</v>
       </c>
@@ -6228,7 +6229,7 @@
       <c r="H8" s="2">
         <v>5000</v>
       </c>
-      <c r="I8" s="78" t="s">
+      <c r="I8" s="75" t="s">
         <v>54</v>
       </c>
       <c r="J8" s="12" t="s">
@@ -6238,7 +6239,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="45.75">
       <c r="B9" s="7"/>
       <c r="D9" s="6">
         <v>1624000</v>
@@ -6255,12 +6256,12 @@
       <c r="H9" s="6">
         <v>50000</v>
       </c>
-      <c r="I9" s="78"/>
+      <c r="I9" s="75"/>
       <c r="J9" s="12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="60.75">
       <c r="B10" s="7"/>
       <c r="D10" s="6">
         <v>753600</v>
@@ -6277,7 +6278,7 @@
       <c r="H10" s="2">
         <v>100</v>
       </c>
-      <c r="I10" s="78"/>
+      <c r="I10" s="75"/>
       <c r="J10" s="12" t="s">
         <v>55</v>
       </c>
@@ -6285,7 +6286,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="60.75">
       <c r="B11" s="7"/>
       <c r="D11" s="6">
         <v>1906800</v>
@@ -6299,7 +6300,7 @@
       <c r="H11" s="2">
         <v>168</v>
       </c>
-      <c r="I11" s="78"/>
+      <c r="I11" s="75"/>
       <c r="J11" s="12" t="s">
         <v>55</v>
       </c>
@@ -6307,7 +6308,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="91.5">
       <c r="B12" s="7"/>
       <c r="D12" s="6">
         <v>682360</v>
@@ -6324,7 +6325,7 @@
       <c r="H12" s="2">
         <v>56</v>
       </c>
-      <c r="I12" s="78"/>
+      <c r="I12" s="75"/>
       <c r="J12" s="12" t="s">
         <v>55</v>
       </c>
@@ -6332,7 +6333,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="106.5">
       <c r="B13" s="7"/>
       <c r="D13" s="6">
         <v>529200</v>
@@ -6349,7 +6350,7 @@
       <c r="H13" s="2">
         <v>56</v>
       </c>
-      <c r="I13" s="78"/>
+      <c r="I13" s="75"/>
       <c r="J13" s="12" t="s">
         <v>55</v>
       </c>
@@ -6357,7 +6358,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="80" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="91.5">
       <c r="B14" s="7"/>
       <c r="D14" s="6">
         <v>1030400</v>
@@ -6374,12 +6375,12 @@
       <c r="H14" s="2">
         <v>100</v>
       </c>
-      <c r="I14" s="78"/>
+      <c r="I14" s="75"/>
       <c r="J14" s="12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="96" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="91.5">
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11">
@@ -6397,7 +6398,7 @@
       <c r="H15" s="10">
         <v>56</v>
       </c>
-      <c r="I15" s="78"/>
+      <c r="I15" s="75"/>
       <c r="J15" s="12" t="s">
         <v>55</v>
       </c>
@@ -6405,7 +6406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="48" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="60.75">
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11">
@@ -6423,7 +6424,7 @@
       <c r="H16" s="10">
         <v>34</v>
       </c>
-      <c r="I16" s="78"/>
+      <c r="I16" s="75"/>
       <c r="J16" s="12" t="s">
         <v>55</v>
       </c>
@@ -6431,7 +6432,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="76.5">
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11">
@@ -6449,7 +6450,7 @@
       <c r="H17" s="10">
         <v>4</v>
       </c>
-      <c r="I17" s="78"/>
+      <c r="I17" s="75"/>
       <c r="J17" s="12" t="s">
         <v>55</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="76.5" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>114</v>
       </c>
@@ -6486,11 +6487,11 @@
       <c r="J18" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="L18" s="86" t="s">
+      <c r="L18" s="83" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="183" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="183" customHeight="1">
       <c r="A19" s="8"/>
       <c r="B19" s="24"/>
       <c r="C19" s="24" t="s">
@@ -6515,12 +6516,12 @@
       <c r="J19" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K19" s="85" t="s">
+      <c r="K19" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="L19" s="86"/>
-    </row>
-    <row r="20" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="L19" s="83"/>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="8"/>
       <c r="B20" s="24"/>
       <c r="C20" s="24" t="s">
@@ -6545,10 +6546,10 @@
       <c r="J20" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K20" s="85"/>
-      <c r="L20" s="86"/>
-    </row>
-    <row r="21" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K20" s="82"/>
+      <c r="L20" s="83"/>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="8"/>
       <c r="B21" s="24"/>
       <c r="C21" s="24" t="s">
@@ -6573,10 +6574,10 @@
       <c r="J21" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K21" s="85"/>
-      <c r="L21" s="86"/>
-    </row>
-    <row r="22" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K21" s="82"/>
+      <c r="L21" s="83"/>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="26"/>
       <c r="B22" s="24"/>
       <c r="C22" s="24" t="s">
@@ -6601,10 +6602,10 @@
       <c r="J22" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K22" s="85"/>
-      <c r="L22" s="86"/>
-    </row>
-    <row r="23" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K22" s="82"/>
+      <c r="L22" s="83"/>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="26"/>
       <c r="B23" s="24"/>
       <c r="C23" s="24" t="s">
@@ -6629,10 +6630,10 @@
       <c r="J23" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K23" s="85"/>
-      <c r="L23" s="86"/>
-    </row>
-    <row r="24" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K23" s="82"/>
+      <c r="L23" s="83"/>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="26"/>
       <c r="B24" s="24"/>
       <c r="C24" s="24" t="s">
@@ -6657,10 +6658,10 @@
       <c r="J24" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K24" s="85"/>
-      <c r="L24" s="86"/>
-    </row>
-    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K24" s="82"/>
+      <c r="L24" s="83"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="26"/>
       <c r="B25" s="24"/>
       <c r="C25" s="24" t="s">
@@ -6685,10 +6686,10 @@
       <c r="J25" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="85"/>
-      <c r="L25" s="86"/>
-    </row>
-    <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K25" s="82"/>
+      <c r="L25" s="83"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="26"/>
       <c r="B26" s="24"/>
       <c r="C26" s="24" t="s">
@@ -6713,10 +6714,10 @@
       <c r="J26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K26" s="85"/>
-      <c r="L26" s="86"/>
-    </row>
-    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K26" s="82"/>
+      <c r="L26" s="83"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="26"/>
       <c r="B27" s="24"/>
       <c r="C27" s="24" t="s">
@@ -6741,10 +6742,10 @@
       <c r="J27" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K27" s="85"/>
-      <c r="L27" s="86"/>
-    </row>
-    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K27" s="82"/>
+      <c r="L27" s="83"/>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="26"/>
       <c r="B28" s="24"/>
       <c r="C28" s="24" t="s">
@@ -6769,10 +6770,10 @@
       <c r="J28" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K28" s="85"/>
-      <c r="L28" s="86"/>
-    </row>
-    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="K28" s="82"/>
+      <c r="L28" s="83"/>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="26"/>
       <c r="B29" s="24"/>
       <c r="C29" s="24" t="s">
@@ -6797,9 +6798,9 @@
       <c r="J29" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K29" s="85"/>
-    </row>
-    <row r="30" spans="1:12" ht="100.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K29" s="82"/>
+    </row>
+    <row r="30" spans="1:12" ht="100.5" customHeight="1">
       <c r="A30" s="17">
         <v>112026</v>
       </c>
@@ -6835,7 +6836,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -6846,7 +6847,7 @@
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -6857,7 +6858,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6866,7 +6867,7 @@
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -6877,7 +6878,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -6888,7 +6889,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -6899,7 +6900,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -6910,7 +6911,7 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -6921,7 +6922,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -6932,7 +6933,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -6943,7 +6944,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -6954,7 +6955,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -6965,7 +6966,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -6976,7 +6977,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -6987,7 +6988,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -6998,7 +6999,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -7009,7 +7010,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -7020,7 +7021,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -7031,7 +7032,7 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -7042,7 +7043,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -7053,7 +7054,7 @@
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -7064,7 +7065,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -7075,7 +7076,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -7086,7 +7087,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -7097,7 +7098,7 @@
       <c r="H54" s="8"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -7108,7 +7109,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -7119,7 +7120,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -7130,7 +7131,7 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -7141,7 +7142,7 @@
       <c r="H58" s="8"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -7152,7 +7153,7 @@
       <c r="H59" s="8"/>
       <c r="I59" s="8"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -7163,7 +7164,7 @@
       <c r="H60" s="8"/>
       <c r="I60" s="8"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -7174,7 +7175,7 @@
       <c r="H61" s="8"/>
       <c r="I61" s="8"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -7185,7 +7186,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -7196,7 +7197,7 @@
       <c r="H63" s="8"/>
       <c r="I63" s="8"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -7207,7 +7208,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -7218,7 +7219,7 @@
       <c r="H65" s="8"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -7229,7 +7230,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -7240,7 +7241,7 @@
       <c r="H67" s="8"/>
       <c r="I67" s="8"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -7251,7 +7252,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -7297,12 +7298,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="52.6640625" customWidth="1"/>
+    <col min="1" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="59" t="s">
         <v>4</v>
       </c>
@@ -7310,171 +7311,171 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="75" t="s">
+    <row r="2" spans="1:2" ht="45.75">
+      <c r="A2" s="84" t="s">
         <v>39</v>
       </c>
       <c r="B2" s="60" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="75" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="84" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="60" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="75" t="s">
+    <row r="4" spans="1:2" ht="30.75">
+      <c r="A4" s="84" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="60" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="75" t="s">
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="84" t="s">
         <v>123</v>
       </c>
       <c r="B5" s="60" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="96" x14ac:dyDescent="0.2">
-      <c r="A6" s="75" t="s">
+    <row r="6" spans="1:2" ht="91.5">
+      <c r="A6" s="84" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="60" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="75" t="s">
+    <row r="7" spans="1:2" ht="45.75">
+      <c r="A7" s="84" t="s">
         <v>73</v>
       </c>
       <c r="B7" s="60" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8" s="75" t="s">
+    <row r="8" spans="1:2" ht="45.75">
+      <c r="A8" s="84" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="60" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="75" t="s">
+    <row r="9" spans="1:2" ht="45.75">
+      <c r="A9" s="84" t="s">
         <v>74</v>
       </c>
       <c r="B9" s="60" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A10" s="75" t="s">
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="84" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="85" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="75" t="s">
+    <row r="11" spans="1:2" ht="30.75">
+      <c r="A11" s="84" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="85" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="75" t="s">
+    <row r="12" spans="1:2" ht="45.75">
+      <c r="A12" s="84" t="s">
         <v>133</v>
       </c>
       <c r="B12" s="60" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="75" t="s">
+    <row r="13" spans="1:2" ht="30.75">
+      <c r="A13" s="84" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="85" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="75" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="85" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="75" t="s">
+    <row r="15" spans="1:2" ht="30.75">
+      <c r="A15" s="84" t="s">
         <v>139</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="85" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="75" t="s">
+    <row r="16" spans="1:2" ht="30.75">
+      <c r="A16" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="85" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="75" t="s">
+    <row r="17" spans="1:2" ht="30.75">
+      <c r="A17" s="84" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="60" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A18" s="75" t="s">
+    <row r="18" spans="1:2" ht="30.75">
+      <c r="A18" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="85" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="64" x14ac:dyDescent="0.2">
-      <c r="A19" s="75" t="s">
+    <row r="19" spans="1:2" ht="76.5">
+      <c r="A19" s="84" t="s">
         <v>144</v>
       </c>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="85" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="75" t="s">
+    <row r="20" spans="1:2" ht="30.75">
+      <c r="A20" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="85" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="75" t="s">
+    <row r="21" spans="1:2" ht="45.75">
+      <c r="A21" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="86" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="75" t="s">
+    <row r="22" spans="1:2" ht="30.75">
+      <c r="A22" s="84" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="85" t="s">
         <v>149</v>
       </c>
     </row>
@@ -7484,6 +7485,69 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <UserInfo>
+        <DisplayName>Pem Wangdi</DisplayName>
+        <AccountId>1587</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Adnan Cheema</DisplayName>
+        <AccountId>1811</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Akiko Yamamoto</DisplayName>
+        <AccountId>84</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Riad Meddeb</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Benjamin Keller</DisplayName>
+        <AccountId>1227</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Stefano Pistolese</DisplayName>
+        <AccountId>772</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Saw Win Myo San</DisplayName>
+        <AccountId>1588</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Kyaw Zin Aung Soe</DisplayName>
+        <AccountId>2010</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Jessie Ponce</DisplayName>
+        <AccountId>1809</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Lat Lat Aye</DisplayName>
+        <AccountId>1834</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7492,9 +7556,9 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -7519,6 +7583,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -7598,6 +7663,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -7741,103 +7811,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-    <SharedWithUsers xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59">
-      <UserInfo>
-        <DisplayName>Pem Wangdi</DisplayName>
-        <AccountId>1587</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Adnan Cheema</DisplayName>
-        <AccountId>1811</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Akiko Yamamoto</DisplayName>
-        <AccountId>84</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Riad Meddeb</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Benjamin Keller</DisplayName>
-        <AccountId>1227</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Stefano Pistolese</DisplayName>
-        <AccountId>772</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Saw Win Myo San</DisplayName>
-        <AccountId>1588</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Kyaw Zin Aung Soe</DisplayName>
-        <AccountId>2010</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Jessie Ponce</DisplayName>
-        <AccountId>1809</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Lat Lat Aye</DisplayName>
-        <AccountId>1834</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7AE853E-4F37-4A3C-B15C-49DE17FB657C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87DAB1ED-73B6-46CD-978D-DDC5D0F3F477}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83981D53-9EA2-4F8A-A632-D9F3E2E44328}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
-    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7AE853E-4F37-4A3C-B15C-49DE17FB657C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87DAB1ED-73B6-46CD-978D-DDC5D0F3F477}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
-    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFBEADC0-4F19-45ED-914F-1FFE20B7C773}"/>
 </file>
--- a/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="11_10448CB3BBC8A79A89107E47BA0E9DE9642947D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6606264-F8AF-4CC0-91FA-4D33866BF24B}"/>
+  <xr:revisionPtr revIDLastSave="619" documentId="11_10448CB3BBC8A79A89107E47BA0E9DE9642947D6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E772FFED-6FB8-41F2-98AA-20C325822967}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (4)" sheetId="5" r:id="rId1"/>
-    <sheet name="Projects (3)" sheetId="4" r:id="rId2"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId3"/>
-    <sheet name="Projects" sheetId="1" r:id="rId4"/>
+    <sheet name="Projects (3)" sheetId="5" r:id="rId1"/>
+    <sheet name="Projects (2.5)" sheetId="4" r:id="rId2"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId4"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -42,15 +42,108 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={DFF87492-011A-4DFF-B2A2-0767EFA86F14}</author>
+    <author>Folashade Jaiyeola</author>
+    <author>tc={079A32D1-D600-4A60-B4CE-F2D4598DC6F2}</author>
     <author>tc={32BF67D8-AF94-4243-BB0C-9121426D1E0C}</author>
+    <author>tc={2D8B2591-10A3-4BD9-800A-1F7644AFF05C}</author>
+    <author>tc={A0D25A78-FA1F-4143-B02D-7892CF711E91}</author>
   </authors>
   <commentList>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{32BF67D8-AF94-4243-BB0C-9121426D1E0C}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{DFF87492-011A-4DFF-B2A2-0767EFA86F14}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @Stefano Pistolese  this is project is now cancelled in accordance's with GEF's directives</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="1" shapeId="0" xr:uid="{1246582D-C5F4-4BEC-8963-6EF02F580323}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Folashade Jaiyeola:
+Former: 2.89
+Deleted because project has been cancelled</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="2" shapeId="0" xr:uid="{079A32D1-D600-4A60-B4CE-F2D4598DC6F2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @Stefano Pistolese  project is now operationally closed</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="1" shapeId="0" xr:uid="{298E4CA3-1DFA-44BB-B053-BB9F9573A50E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Folashade Jaiyeola:
+We should not include this project as it is not fully approved
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="3" shapeId="0" xr:uid="{32BF67D8-AF94-4243-BB0C-9121426D1E0C}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     @Stefano Pistolese the CO is no longer pursuing this partnership. We can remove it from here. Noted that all your questions are related to this particular project. </t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="1" shapeId="0" xr:uid="{7AAC13A1-15C3-451D-B27F-DC8FFD801409}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Folashade Jaiyeola:
+We should not include this project as it is still in approval stage
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="4" shapeId="0" xr:uid="{2D8B2591-10A3-4BD9-800A-1F7644AFF05C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @Stefano Pistolese  project is now operationally closed</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="5" shapeId="0" xr:uid="{A0D25A78-FA1F-4143-B02D-7892CF711E91}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+[Tasks]
+There is a task anchored to this comment that cannot be viewed in your client.
+Comment:
+    @Stefano Pistolese new</t>
       </text>
     </comment>
   </commentList>
@@ -76,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="168">
   <si>
     <t>Project ID</t>
   </si>
@@ -139,6 +232,9 @@
   </si>
   <si>
     <t>Policy Population</t>
+  </si>
+  <si>
+    <t>Project Document</t>
   </si>
   <si>
     <t>(Suspended until Nov 2023) Rural Renewable Energy</t>
@@ -168,6 +264,9 @@
   </si>
   <si>
     <t>Some Sources</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
   <si>
     <t>GHG Emissions Reduction</t>
@@ -264,28 +363,44 @@
     <t xml:space="preserve">Number of HH provided with Solar home lighting systems </t>
   </si>
   <si>
-    <t>the project document was developed and resources in pipeline.</t>
+    <t>the project document was developed and resources in pipeline.
+Projected target: 5000</t>
   </si>
   <si>
     <t>in search of donor</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>number of HHs provided with energy efficient cookstoves</t>
   </si>
   <si>
+    <t>Projected target: 50000</t>
+  </si>
+  <si>
     <t>Water Services</t>
   </si>
   <si>
     <t xml:space="preserve">number of village water supply systems upgraded to solar-powered applications </t>
   </si>
   <si>
+    <t>Projected target: 100</t>
+  </si>
+  <si>
     <t>Estimate # of beneficiaries / village</t>
   </si>
   <si>
     <t>number of villages provided with a new solar-powered village water supply system</t>
   </si>
   <si>
+    <t>Projected target: 168</t>
+  </si>
+  <si>
     <t xml:space="preserve">number of villages provided with a new small-scale solar irrigation system to improve agricultural production </t>
+  </si>
+  <si>
+    <t>Projected target: 56</t>
   </si>
   <si>
     <t>number of small-scale irrigation systems upgraded to solar-powered applications to improve the efficiency of agricultural production</t>
@@ -307,7 +422,13 @@
     <t>number of villages supported for connection to a nearby mini-grid</t>
   </si>
   <si>
+    <t>Projected target: 34</t>
+  </si>
+  <si>
     <t>number of new mini-grid systems tested to support livelihood recovery in broader areas</t>
+  </si>
+  <si>
+    <t>Projected target: 4</t>
   </si>
   <si>
     <r>
@@ -352,6 +473,9 @@
   </si>
   <si>
     <t>Promoting the use of solar technologies for agricultural and rural development in Cambodia and Myanmar</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00112026</t>
   </si>
   <si>
     <t>Number of households provided agricultural service and Solar Water Pumping Systems</t>
@@ -389,6 +513,27 @@
     <t>Ongoing</t>
   </si>
   <si>
+    <t>UNDP-CFPII Renewable Energy Interventions (concept note submitted)</t>
+  </si>
+  <si>
+    <t>Number of households with access to energy through with solar home systems</t>
+  </si>
+  <si>
+    <t>Projected target: 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of women livelihoods groups whose productive efficiency have improved through PUE inputs  </t>
+  </si>
+  <si>
+    <t>Projected target: 20</t>
+  </si>
+  <si>
+    <t>Number of villages with improved lighting, water supply and irrigation services through solar/RE applications</t>
+  </si>
+  <si>
+    <t>Projected target: 10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Comments </t>
   </si>
   <si>
@@ -439,6 +584,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">3 villages in Shan state were supported with 1 solar pumping system and 2 solar bubble dryers. 
 </t>
@@ -448,6 +594,7 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>Solar pumping - 15 HH
 Solar dryers - 30 HH in total (two villages)</t>
@@ -457,6 +604,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -487,6 +635,9 @@
     </r>
   </si>
   <si>
+    <t>the project document was developed and resources in pipeline.</t>
+  </si>
+  <si>
     <t>This appears ok</t>
   </si>
   <si>
@@ -638,7 +789,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -650,6 +801,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -716,21 +868,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -746,7 +883,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -754,7 +891,16 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
@@ -909,7 +1055,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -974,9 +1120,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -988,16 +1131,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1006,7 +1149,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1018,15 +1161,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1039,7 +1179,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1079,12 +1219,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1123,18 +1257,57 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1147,17 +1320,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1177,8 +1341,126 @@
 </styleSheet>
 </file>
 
+<file path=xl/documenttasks/documenttask1.xml><?xml version="1.0" encoding="utf-8"?>
+<Tasks xmlns="http://schemas.microsoft.com/office/tasks/2019/documenttasks">
+  <Task id="{5A12020A-27B1-4CA9-B650-CC2A35AD9D4A}">
+    <Anchor>
+      <Comment id="{079A32D1-D600-4A60-B4CE-F2D4598DC6F2}"/>
+    </Anchor>
+    <History>
+      <Event time="2024-11-07T08:57:29.54" id="{8E84F27A-1EB6-41BF-AB9C-F8B3E1D8D419}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{079A32D1-D600-4A60-B4CE-F2D4598DC6F2}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2024-11-07T08:57:29.54" id="{15065B26-8402-4166-979C-EE1467D704D1}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{079A32D1-D600-4A60-B4CE-F2D4598DC6F2}"/>
+        </Anchor>
+        <Assign userId="S::stefano.pistolese@undp.org::a561415f-6f58-4f47-821a-08ad5d654fc1" userName="Stefano Pistolese" userProvider="AD"/>
+      </Event>
+      <Event time="2024-11-07T08:57:29.54" id="{90CB696A-C23A-4615-817F-41A0CB76133B}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{079A32D1-D600-4A60-B4CE-F2D4598DC6F2}"/>
+        </Anchor>
+        <SetTitle title="@Stefano Pistolese project is now operationally closed"/>
+      </Event>
+    </History>
+  </Task>
+  <Task id="{EBD83B0C-36C0-41FE-AA23-C204CB408C8E}">
+    <Anchor>
+      <Comment id="{2D8B2591-10A3-4BD9-800A-1F7644AFF05C}"/>
+    </Anchor>
+    <History>
+      <Event time="2024-11-07T08:58:17.06" id="{F61B0B77-CA2D-481C-91E0-631B584AE3D5}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{2D8B2591-10A3-4BD9-800A-1F7644AFF05C}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2024-11-07T08:58:17.06" id="{1246BF3E-7D5D-4A77-B5F9-70C51EE97CD4}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{2D8B2591-10A3-4BD9-800A-1F7644AFF05C}"/>
+        </Anchor>
+        <Assign userId="S::stefano.pistolese@undp.org::a561415f-6f58-4f47-821a-08ad5d654fc1" userName="Stefano Pistolese" userProvider="AD"/>
+      </Event>
+      <Event time="2024-11-07T08:58:17.06" id="{FEDA641F-C5CF-49B4-B6F3-8DBAB80160DC}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{2D8B2591-10A3-4BD9-800A-1F7644AFF05C}"/>
+        </Anchor>
+        <SetTitle title="@Stefano Pistolese project is now operationally closed"/>
+      </Event>
+    </History>
+  </Task>
+  <Task id="{CA867E87-9A24-47B0-A05C-E76A74136A13}">
+    <Anchor>
+      <Comment id="{DFF87492-011A-4DFF-B2A2-0767EFA86F14}"/>
+    </Anchor>
+    <History>
+      <Event time="2024-11-07T08:56:57.70" id="{861A3438-F247-4C60-AA54-EC2339E57B0D}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{DFF87492-011A-4DFF-B2A2-0767EFA86F14}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2024-11-07T08:56:57.70" id="{2CB25B52-2467-4B68-B020-0543760A0B7D}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{DFF87492-011A-4DFF-B2A2-0767EFA86F14}"/>
+        </Anchor>
+        <Assign userId="S::stefano.pistolese@undp.org::a561415f-6f58-4f47-821a-08ad5d654fc1" userName="Stefano Pistolese" userProvider="AD"/>
+      </Event>
+      <Event time="2024-11-07T08:56:57.70" id="{3142056C-7534-4BB3-AF25-BA12F6C880BF}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{DFF87492-011A-4DFF-B2A2-0767EFA86F14}"/>
+        </Anchor>
+        <SetTitle title="@Stefano Pistolese this is project is now cancelled in accordance's with GEF's directives"/>
+      </Event>
+    </History>
+  </Task>
+  <Task id="{97F1429E-1AB6-46B0-81B1-711A7760F3F0}">
+    <Anchor>
+      <Comment id="{A0D25A78-FA1F-4143-B02D-7892CF711E91}"/>
+    </Anchor>
+    <History>
+      <Event time="2024-11-07T09:07:04.07" id="{AEB1C5A3-D144-4807-9FF1-48DCCC399438}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{A0D25A78-FA1F-4143-B02D-7892CF711E91}"/>
+        </Anchor>
+        <Create/>
+      </Event>
+      <Event time="2024-11-07T09:07:04.07" id="{BCE016BB-B3F6-4835-86B5-9C7E541880E5}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{A0D25A78-FA1F-4143-B02D-7892CF711E91}"/>
+        </Anchor>
+        <Assign userId="S::stefano.pistolese@undp.org::a561415f-6f58-4f47-821a-08ad5d654fc1" userName="Stefano Pistolese" userProvider="AD"/>
+      </Event>
+      <Event time="2024-11-07T09:07:04.07" id="{BCE88D72-3C5D-4836-85BF-E854666640BE}">
+        <Attribution userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" userName="Pem Wangdi" userProvider="AD"/>
+        <Anchor>
+          <Comment id="{A0D25A78-FA1F-4143-B02D-7892CF711E91}"/>
+        </Anchor>
+        <SetTitle title="@Stefano Pistolese new"/>
+      </Event>
+    </History>
+  </Task>
+</Tasks>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Pem Wangdi" id="{460FBBF0-6E76-4FD1-BD4D-7D559C8DF731}" userId="Pem Wangdi" providerId="None"/>
   <person displayName="Stefano Pistolese" id="{EADE5D7D-8870-4C43-B060-974FE98BE228}" userId="stefano.pistolese@undp.org" providerId="PeoplePicker"/>
   <person displayName="Pem Wangdi" id="{73E060E6-284D-4475-A5CB-8B4D35EDBBD0}" userId="S::pem.wangdi@undp.org::50c260e5-b28c-40ff-975c-dba543e9dc3c" providerId="AD"/>
 </personList>
@@ -1471,10 +1753,34 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B2" dT="2024-11-07T08:56:57.70" personId="{460FBBF0-6E76-4FD1-BD4D-7D559C8DF731}" id="{DFF87492-011A-4DFF-B2A2-0767EFA86F14}">
+    <text>@Stefano Pistolese  this is project is now cancelled in accordance's with GEF's directives</text>
+    <mentions>
+      <mention mentionpersonId="{EADE5D7D-8870-4C43-B060-974FE98BE228}" mentionId="{3C412890-F8D4-4EEC-9AB0-76C778CE6B60}" startIndex="0" length="18"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="B5" dT="2024-11-07T08:57:29.54" personId="{460FBBF0-6E76-4FD1-BD4D-7D559C8DF731}" id="{079A32D1-D600-4A60-B4CE-F2D4598DC6F2}">
+    <text>@Stefano Pistolese  project is now operationally closed</text>
+    <mentions>
+      <mention mentionpersonId="{EADE5D7D-8870-4C43-B060-974FE98BE228}" mentionId="{8F62E06E-EE88-413A-BCBE-0DBE4F9A5072}" startIndex="0" length="18"/>
+    </mentions>
+  </threadedComment>
   <threadedComment ref="I8" dT="2023-11-19T02:36:28.85" personId="{73E060E6-284D-4475-A5CB-8B4D35EDBBD0}" id="{32BF67D8-AF94-4243-BB0C-9121426D1E0C}">
     <text xml:space="preserve">@Stefano Pistolese the CO is no longer pursuing this partnership. We can remove it from here. Noted that all your questions are related to this particular project. </text>
     <mentions>
       <mention mentionpersonId="{EADE5D7D-8870-4C43-B060-974FE98BE228}" mentionId="{1BFAA6E2-4CE3-4F0D-AB0A-408510143880}" startIndex="0" length="18"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="B30" dT="2024-11-07T08:58:17.06" personId="{460FBBF0-6E76-4FD1-BD4D-7D559C8DF731}" id="{2D8B2591-10A3-4BD9-800A-1F7644AFF05C}">
+    <text>@Stefano Pistolese  project is now operationally closed</text>
+    <mentions>
+      <mention mentionpersonId="{EADE5D7D-8870-4C43-B060-974FE98BE228}" mentionId="{B924C2E3-319D-4797-B303-209FACBCAAC5}" startIndex="0" length="18"/>
+    </mentions>
+  </threadedComment>
+  <threadedComment ref="B31" dT="2024-11-07T09:07:04.07" personId="{460FBBF0-6E76-4FD1-BD4D-7D559C8DF731}" id="{A0D25A78-FA1F-4143-B02D-7892CF711E91}">
+    <text>@Stefano Pistolese new</text>
+    <mentions>
+      <mention mentionpersonId="{EADE5D7D-8870-4C43-B060-974FE98BE228}" mentionId="{7B442D3F-A555-429B-9C97-20A64ABA4AF5}" startIndex="0" length="18"/>
     </mentions>
   </threadedComment>
 </ThreadedComments>
@@ -1511,10 +1817,12 @@
     <col min="14" max="14" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="18" width="9.140625" style="2"/>
     <col min="19" max="19" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="2"/>
+    <col min="20" max="21" width="9.140625" style="2"/>
+    <col min="22" max="22" width="16.140625" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" ht="35.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,301 +1853,311 @@
       <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="69" t="s">
+      <c r="K1" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="61" t="s">
+      <c r="L1" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="62" t="s">
+      <c r="M1" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="61" t="s">
+      <c r="N1" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="61" t="s">
+      <c r="O1" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="62" t="s">
+      <c r="P1" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="62" t="s">
+      <c r="Q1" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="63" t="s">
+      <c r="R1" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="64" t="s">
+      <c r="S1" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="63" t="s">
+      <c r="T1" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="64" t="s">
+      <c r="U1" s="60" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="76" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" spans="1:23" ht="139.5" customHeight="1">
-      <c r="A2" s="58">
+      <c r="A2" s="56">
         <v>104187</v>
       </c>
-      <c r="B2" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="70" t="s">
+      <c r="B2" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="58">
+      <c r="C2" s="66" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="56">
         <v>4934228</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="4">
-        <v>2.89</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="62"/>
+      <c r="N2" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="62"/>
+      <c r="S2" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="62"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="75">
+      <c r="E3" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="L2" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="66"/>
-      <c r="N2" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" s="66"/>
-      <c r="U2" s="68"/>
-    </row>
-    <row r="3" spans="1:23" ht="60.75">
-      <c r="E3" s="71" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="H3" s="2">
         <v>20508</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="66"/>
-      <c r="N3" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="68"/>
-      <c r="T3" s="66"/>
-      <c r="U3" s="68"/>
-    </row>
-    <row r="4" spans="1:23" ht="76.5">
+      <c r="M3" s="62"/>
+      <c r="N3" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="62"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="62"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="62"/>
+      <c r="U3" s="64"/>
+    </row>
+    <row r="4" spans="1:23" ht="75">
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="68"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="68"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="64"/>
     </row>
     <row r="5" spans="1:23" ht="91.5">
       <c r="A5" s="2">
         <v>111777</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2">
         <v>716641</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L5" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="66"/>
-      <c r="R5" s="66"/>
-      <c r="S5" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="66"/>
-      <c r="U5" s="68"/>
-    </row>
-    <row r="6" spans="1:23" ht="106.5">
+      <c r="L5" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M5" s="62"/>
+      <c r="N5" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" s="62"/>
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="62"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="105">
       <c r="C6" s="3"/>
       <c r="D6" s="5"/>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="66"/>
-      <c r="N6" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="66"/>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="66"/>
-      <c r="S6" s="68"/>
-      <c r="T6" s="66"/>
-      <c r="U6" s="68"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="62"/>
+      <c r="P6" s="62"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="62"/>
+      <c r="S6" s="64"/>
+      <c r="T6" s="62"/>
+      <c r="U6" s="64"/>
     </row>
     <row r="7" spans="1:23" ht="244.5">
       <c r="C7" s="3"/>
       <c r="D7" s="5"/>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>49</v>
+        <v>26</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="66"/>
-      <c r="N7" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="68"/>
-      <c r="T7" s="66"/>
-      <c r="U7" s="68"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="64"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="64"/>
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" ht="45.75">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>52</v>
+      <c r="A8" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="82" t="s">
+        <v>54</v>
       </c>
       <c r="D8" s="6">
         <v>1348200</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I8" s="75" t="s">
-        <v>54</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="66"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="68" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="66"/>
-      <c r="U8" s="68"/>
+        <v>57</v>
+      </c>
+      <c r="L8" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="62"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="62"/>
+      <c r="P8" s="62"/>
+      <c r="Q8" s="62"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="T8" s="62"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:23" ht="45.75">
       <c r="B9" s="7"/>
@@ -1847,31 +2165,33 @@
         <v>1624000</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="6">
-        <v>50000</v>
-      </c>
-      <c r="I9" s="75"/>
-      <c r="J9" s="72"/>
-      <c r="L9" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M9" s="66"/>
-      <c r="N9" s="67"/>
-      <c r="O9" s="66"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="66"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="66"/>
-      <c r="U9" s="68"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="68"/>
+      <c r="L9" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="62"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="62"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="64"/>
     </row>
     <row r="10" spans="1:23" ht="76.5">
       <c r="B10" s="7"/>
@@ -1879,33 +2199,35 @@
         <v>753600</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="12">
-        <v>100</v>
-      </c>
-      <c r="I10" s="75"/>
-      <c r="J10" s="72"/>
-      <c r="L10" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="66"/>
-      <c r="N10" s="67"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="68"/>
-      <c r="T10" s="66"/>
-      <c r="U10" s="68"/>
-      <c r="W10" s="28" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="68"/>
+      <c r="L10" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="62"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="62"/>
+      <c r="P10" s="62"/>
+      <c r="Q10" s="62"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="62"/>
+      <c r="U10" s="64"/>
+      <c r="W10" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="76.5">
@@ -1914,31 +2236,33 @@
         <v>1906800</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12">
-        <v>168</v>
-      </c>
-      <c r="I11" s="75"/>
-      <c r="J11" s="72"/>
-      <c r="L11" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="66"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="66"/>
-      <c r="R11" s="66"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="66"/>
-      <c r="U11" s="68"/>
-      <c r="W11" s="28" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="68"/>
+      <c r="L11" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="62"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="64"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="64"/>
+      <c r="W11" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="91.5">
@@ -1947,33 +2271,35 @@
         <v>682360</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="12">
-        <v>56</v>
-      </c>
-      <c r="I12" s="75"/>
-      <c r="J12" s="72"/>
-      <c r="L12" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M12" s="66"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="68"/>
-      <c r="W12" s="28" t="s">
-        <v>59</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="68"/>
+      <c r="L12" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="62"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="62"/>
+      <c r="R12" s="62"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="62"/>
+      <c r="U12" s="64"/>
+      <c r="W12" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="106.5">
@@ -1982,33 +2308,35 @@
         <v>529200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="12">
-        <v>56</v>
-      </c>
-      <c r="I13" s="75"/>
-      <c r="J13" s="72"/>
-      <c r="L13" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="66"/>
-      <c r="N13" s="67"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="66"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="66"/>
-      <c r="U13" s="68"/>
-      <c r="W13" s="28" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J13" s="68"/>
+      <c r="L13" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" s="62"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
+      <c r="R13" s="62"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="62"/>
+      <c r="U13" s="64"/>
+      <c r="W13" s="27" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="91.5">
@@ -2017,31 +2345,33 @@
         <v>1030400</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="12">
-        <v>100</v>
-      </c>
-      <c r="I14" s="75"/>
-      <c r="J14" s="72"/>
-      <c r="L14" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M14" s="66"/>
-      <c r="N14" s="67"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="66"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="68"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="68"/>
+      <c r="L14" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="62"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="64"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="64"/>
     </row>
     <row r="15" spans="1:23" ht="91.5">
       <c r="B15" s="9"/>
@@ -2050,33 +2380,35 @@
         <v>599760</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="74">
-        <v>56</v>
-      </c>
-      <c r="I15" s="75"/>
-      <c r="J15" s="72"/>
-      <c r="L15" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="66"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="68"/>
-      <c r="W15" s="28" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="69" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="70">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="68"/>
+      <c r="L15" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="62"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="64"/>
+      <c r="T15" s="62"/>
+      <c r="U15" s="64"/>
+      <c r="W15" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="76.5">
@@ -2086,33 +2418,35 @@
         <v>299540</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="74" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="74">
-        <v>34</v>
-      </c>
-      <c r="I16" s="75"/>
-      <c r="J16" s="72"/>
-      <c r="L16" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" s="66"/>
-      <c r="N16" s="67"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="68"/>
-      <c r="W16" s="28" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="F16" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="70">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J16" s="68"/>
+      <c r="L16" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="62"/>
+      <c r="N16" s="63"/>
+      <c r="O16" s="62"/>
+      <c r="P16" s="62"/>
+      <c r="Q16" s="62"/>
+      <c r="R16" s="62"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="62"/>
+      <c r="U16" s="64"/>
+      <c r="W16" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="76.5">
@@ -2122,528 +2456,581 @@
         <v>1205640</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>76</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" s="10">
-        <v>4</v>
-      </c>
-      <c r="I17" s="75"/>
-      <c r="J17" s="72"/>
-      <c r="L17" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M17" s="66"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="66"/>
-      <c r="U17" s="68"/>
-      <c r="W17" s="28" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="68"/>
+      <c r="L17" s="61" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="62"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="62"/>
+      <c r="P17" s="62"/>
+      <c r="Q17" s="62"/>
+      <c r="R17" s="62"/>
+      <c r="S17" s="64"/>
+      <c r="T17" s="62"/>
+      <c r="U17" s="64"/>
+      <c r="W17" s="27" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="60.75">
-      <c r="B18" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>71</v>
+      <c r="A18" s="12"/>
+      <c r="B18" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="65"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="66"/>
-      <c r="U18" s="68"/>
+        <v>57</v>
+      </c>
+      <c r="L18" s="61"/>
+      <c r="M18" s="62"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="62"/>
+      <c r="P18" s="62"/>
+      <c r="Q18" s="62"/>
+      <c r="R18" s="62"/>
+      <c r="S18" s="64"/>
+      <c r="T18" s="62"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="8"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>71</v>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I19" s="8"/>
-      <c r="J19" s="72"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="66"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="66"/>
-      <c r="U19" s="68"/>
-      <c r="W19" s="27" t="s">
-        <v>72</v>
+      <c r="J19" s="68"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="62"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="62"/>
+      <c r="Q19" s="62"/>
+      <c r="R19" s="62"/>
+      <c r="S19" s="64"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="64"/>
+      <c r="W19" s="26" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:23">
       <c r="A20" s="8"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>71</v>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I20" s="8"/>
-      <c r="J20" s="72"/>
-      <c r="L20" s="65"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="66"/>
-      <c r="U20" s="68"/>
+      <c r="J20" s="68"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="62"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="62"/>
+      <c r="R20" s="62"/>
+      <c r="S20" s="64"/>
+      <c r="T20" s="62"/>
+      <c r="U20" s="64"/>
     </row>
     <row r="21" spans="1:23">
       <c r="A21" s="8"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>71</v>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I21" s="8"/>
-      <c r="J21" s="72"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="L21" s="61"/>
+      <c r="M21" s="62"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="62"/>
+      <c r="P21" s="62"/>
+      <c r="Q21" s="62"/>
+      <c r="R21" s="62"/>
+      <c r="S21" s="64"/>
+      <c r="T21" s="62"/>
+      <c r="U21" s="64"/>
     </row>
     <row r="22" spans="1:23">
-      <c r="A22" s="26"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>71</v>
+      <c r="A22" s="25"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I22" s="8"/>
-      <c r="J22" s="72"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="68"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="L22" s="61"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="64"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="64"/>
     </row>
     <row r="23" spans="1:23">
-      <c r="A23" s="26"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>71</v>
+      <c r="A23" s="25"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I23" s="8"/>
-      <c r="J23" s="72"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="66"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66"/>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="L23" s="61"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="64"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="64"/>
     </row>
     <row r="24" spans="1:23">
-      <c r="A24" s="26"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>71</v>
+      <c r="A24" s="25"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I24" s="8"/>
-      <c r="J24" s="72"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="67"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="68"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="L24" s="61"/>
+      <c r="M24" s="62"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="62"/>
+      <c r="P24" s="62"/>
+      <c r="Q24" s="62"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="64"/>
+      <c r="T24" s="62"/>
+      <c r="U24" s="64"/>
     </row>
     <row r="25" spans="1:23">
-      <c r="A25" s="26"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>71</v>
+      <c r="A25" s="25"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I25" s="8"/>
-      <c r="J25" s="72"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="68"/>
+      <c r="J25" s="68"/>
+      <c r="L25" s="61"/>
+      <c r="M25" s="62"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="62"/>
+      <c r="S25" s="64"/>
+      <c r="T25" s="62"/>
+      <c r="U25" s="64"/>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="26"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>71</v>
+      <c r="A26" s="25"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I26" s="8"/>
-      <c r="J26" s="72"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="66"/>
-      <c r="P26" s="66"/>
-      <c r="Q26" s="66"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="68"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="L26" s="61"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="62"/>
+      <c r="R26" s="62"/>
+      <c r="S26" s="64"/>
+      <c r="T26" s="62"/>
+      <c r="U26" s="64"/>
     </row>
     <row r="27" spans="1:23">
-      <c r="A27" s="26"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>71</v>
+      <c r="A27" s="25"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I27" s="8"/>
-      <c r="J27" s="72"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="66"/>
-      <c r="Q27" s="66"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="68"/>
-      <c r="T27" s="66"/>
-      <c r="U27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="64"/>
+      <c r="T27" s="62"/>
+      <c r="U27" s="64"/>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="26"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>71</v>
+      <c r="A28" s="25"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I28" s="8"/>
-      <c r="J28" s="72"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="66"/>
-      <c r="P28" s="66"/>
-      <c r="Q28" s="66"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="68"/>
-      <c r="T28" s="66"/>
-      <c r="U28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="L28" s="61"/>
+      <c r="M28" s="62"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="62"/>
+      <c r="P28" s="62"/>
+      <c r="Q28" s="62"/>
+      <c r="R28" s="62"/>
+      <c r="S28" s="64"/>
+      <c r="T28" s="62"/>
+      <c r="U28" s="64"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="26"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="25" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="24" t="s">
-        <v>71</v>
+      <c r="F29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I29" s="8"/>
-      <c r="J29" s="72"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="66"/>
-      <c r="P29" s="66"/>
-      <c r="Q29" s="66"/>
-      <c r="R29" s="66"/>
-      <c r="S29" s="68"/>
-      <c r="T29" s="66"/>
-      <c r="U29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="62"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="62"/>
+      <c r="S29" s="64"/>
+      <c r="T29" s="62"/>
+      <c r="U29" s="64"/>
     </row>
     <row r="30" spans="1:23" ht="100.5" customHeight="1">
       <c r="A30" s="17">
         <v>112026</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="8"/>
+        <v>88</v>
+      </c>
+      <c r="C30" s="83" t="s">
+        <v>89</v>
+      </c>
       <c r="D30" s="16">
         <v>2285334</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" s="20">
         <v>65000</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="L30" s="65" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="66"/>
-      <c r="N30" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="L30" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="O30" s="66"/>
-      <c r="P30" s="66"/>
-      <c r="Q30" s="66"/>
-      <c r="R30" s="66"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="66"/>
-      <c r="U30" s="68"/>
+      <c r="M30" s="62"/>
+      <c r="N30" s="63" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="62"/>
+      <c r="P30" s="62"/>
+      <c r="Q30" s="62"/>
+      <c r="R30" s="62"/>
+      <c r="S30" s="64"/>
+      <c r="T30" s="62"/>
+      <c r="U30" s="64"/>
+      <c r="V30" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="W30" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:23">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" s="18" customFormat="1" ht="60.75">
+      <c r="A31" s="78"/>
+      <c r="B31" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="79"/>
+      <c r="D31" s="80">
+        <v>300000</v>
+      </c>
+      <c r="E31" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="75" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="79">
+        <v>0</v>
+      </c>
+      <c r="I31" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="J31" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="V31" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="91.5">
       <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="B32" s="74"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="74">
+        <v>0</v>
+      </c>
+      <c r="I32" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" spans="1:10" ht="91.5">
+      <c r="B33" s="74"/>
+      <c r="C33" s="74"/>
+      <c r="D33" s="74"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="74">
+        <v>0</v>
+      </c>
+      <c r="I33" s="74" t="s">
+        <v>100</v>
+      </c>
+      <c r="J33" s="27"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -2654,7 +3041,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:10">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -2665,7 +3052,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:10">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -2676,7 +3063,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:10">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -2687,7 +3074,7 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:10">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -2698,7 +3085,7 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:10">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -2709,7 +3096,7 @@
       <c r="H39" s="8"/>
       <c r="I39" s="8"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:10">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -2720,7 +3107,7 @@
       <c r="H40" s="8"/>
       <c r="I40" s="8"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:10">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -2731,7 +3118,7 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:10">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2742,7 +3129,7 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:10">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -2753,7 +3140,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:10">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -2764,7 +3151,7 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:10">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -2775,7 +3162,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:10">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -2786,7 +3173,7 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:10">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -2797,7 +3184,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:10">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -3040,9 +3427,6 @@
       <c r="I69" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="I8:I17"/>
-  </mergeCells>
   <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q30" xr:uid="{97BDBEF4-1FB4-4A0C-B616-B7EE0734E0D2}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
@@ -3056,7 +3440,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O30" xr:uid="{9849B2E0-8A97-4C0A-8949-7D68082FFC00}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L30" xr:uid="{F2F28460-3E1D-4C42-B792-621FFEFFB35A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L31" xr:uid="{F2F28460-3E1D-4C42-B792-621FFEFFB35A}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M30" xr:uid="{E6CEC797-4FDD-48B1-8B7A-2C37B65F0FB0}">
@@ -3075,10 +3459,11 @@
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{B0AF6CF2-8D4B-4CEC-85E4-8B12A2134EF5}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{FFA35887-35FF-4D17-9D33-55C3DA85B8DE}"/>
+    <hyperlink ref="C30" r:id="rId3" xr:uid="{76A42948-8390-4864-B258-3E043C286742}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -3086,7 +3471,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E30</xm:sqref>
+          <xm:sqref>E2:E31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3117,957 +3502,957 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="75">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="L1" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="M1" s="34" t="s">
-        <v>86</v>
+      <c r="K1" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="33" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="225">
-      <c r="A2" s="77">
+      <c r="A2" s="85">
         <v>104187</v>
       </c>
-      <c r="B2" s="77" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="77">
+      <c r="B2" s="85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="85">
         <v>4934228</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="78" t="s">
-        <v>90</v>
-      </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="O2" s="29"/>
+      <c r="F2" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="28"/>
     </row>
     <row r="3" spans="1:15" ht="135">
-      <c r="A3" s="77"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="36" t="s">
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="78"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
+      <c r="F3" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="86"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
     </row>
     <row r="4" spans="1:15" ht="240">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="36" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="78"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
+      <c r="G4" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="86"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
     </row>
     <row r="5" spans="1:15" ht="150">
-      <c r="A5" s="36">
+      <c r="A5" s="35">
         <v>111777</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="36">
+      <c r="B5" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="35">
         <v>716641</v>
       </c>
-      <c r="E5" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="I5" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="38">
+      <c r="E5" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="37">
         <f>D5/827</f>
         <v>866.5550181378477</v>
       </c>
-      <c r="M5" s="34" t="s">
-        <v>95</v>
+      <c r="M5" s="33" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="225">
-      <c r="A6" s="36">
+      <c r="A6" s="35">
         <v>111777</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="39">
+      <c r="B6" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="38">
         <v>716641</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="38">
+      <c r="E6" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="I6" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="37">
         <f>D6/827</f>
         <v>866.5550181378477</v>
       </c>
-      <c r="M6" s="34" t="s">
-        <v>98</v>
+      <c r="M6" s="33" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="255">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>25</v>
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>26</v>
       </c>
       <c r="H7" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="I7" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="41"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
+        <v>116</v>
+      </c>
+      <c r="I7" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="35"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
     </row>
     <row r="8" spans="1:15" ht="60">
-      <c r="A8" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="43">
+      <c r="A8" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="41">
         <v>1348200</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="36">
+      <c r="E8" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="35">
         <v>5000</v>
       </c>
-      <c r="I8" s="76" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K8" s="36"/>
-      <c r="L8" s="34">
+      <c r="I8" s="84" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="L8" s="33">
         <f t="shared" ref="L8:L17" si="0">D8/H8</f>
         <v>269.64</v>
       </c>
-      <c r="M8" s="34" t="s">
-        <v>102</v>
+      <c r="M8" s="33" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="45">
-      <c r="A9" s="36"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="43">
+      <c r="A9" s="35"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="41">
         <v>1624000</v>
       </c>
-      <c r="E9" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="43">
+      <c r="E9" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="41">
         <v>50000</v>
       </c>
-      <c r="I9" s="76"/>
-      <c r="J9" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="36"/>
-      <c r="L9" s="34">
+      <c r="I9" s="84"/>
+      <c r="J9" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="35"/>
+      <c r="L9" s="33">
         <f t="shared" si="0"/>
         <v>32.479999999999997</v>
       </c>
-      <c r="M9" s="34" t="s">
-        <v>103</v>
+      <c r="M9" s="33" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="60">
-      <c r="A10" s="36"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="43">
+      <c r="A10" s="35"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="41">
         <v>753600</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="36">
+      <c r="E10" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="35">
         <v>100</v>
       </c>
-      <c r="I10" s="76"/>
-      <c r="J10" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="34">
+      <c r="I10" s="84"/>
+      <c r="J10" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="33">
         <f t="shared" si="0"/>
         <v>7536</v>
       </c>
-      <c r="M10" s="34" t="s">
-        <v>105</v>
+      <c r="M10" s="33" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="60">
-      <c r="A11" s="36"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="43">
+      <c r="A11" s="35"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="41">
         <v>1906800</v>
       </c>
-      <c r="E11" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36">
+      <c r="E11" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35">
         <v>168</v>
       </c>
-      <c r="I11" s="76"/>
-      <c r="J11" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="34">
+      <c r="I11" s="84"/>
+      <c r="J11" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="33">
         <f t="shared" si="0"/>
         <v>11350</v>
       </c>
-      <c r="M11" s="34" t="s">
-        <v>106</v>
+      <c r="M11" s="33" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="90">
-      <c r="A12" s="36"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="43">
+      <c r="A12" s="35"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="41">
         <v>682360</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="36">
+      <c r="E12" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="35">
         <v>56</v>
       </c>
-      <c r="I12" s="76"/>
-      <c r="J12" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="34">
+      <c r="I12" s="84"/>
+      <c r="J12" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="33">
         <f t="shared" si="0"/>
         <v>12185</v>
       </c>
-      <c r="M12" s="34" t="s">
-        <v>107</v>
+      <c r="M12" s="33" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="135">
-      <c r="A13" s="36"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="43">
+      <c r="A13" s="35"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="41">
         <v>529200</v>
       </c>
-      <c r="E13" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="36">
+      <c r="E13" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="35">
         <v>56</v>
       </c>
-      <c r="I13" s="76"/>
-      <c r="J13" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="34">
+      <c r="I13" s="84"/>
+      <c r="J13" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="33">
         <f t="shared" si="0"/>
         <v>9450</v>
       </c>
-      <c r="M13" s="34" t="s">
-        <v>108</v>
+      <c r="M13" s="33" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="90">
-      <c r="A14" s="36"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="43">
+      <c r="A14" s="35"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="41">
         <v>1030400</v>
       </c>
-      <c r="E14" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="36">
+      <c r="E14" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="35">
         <v>100</v>
       </c>
-      <c r="I14" s="76"/>
-      <c r="J14" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K14" s="36"/>
-      <c r="L14" s="34">
+      <c r="I14" s="84"/>
+      <c r="J14" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K14" s="35"/>
+      <c r="L14" s="33">
         <f t="shared" si="0"/>
         <v>10304</v>
       </c>
-      <c r="M14" s="34" t="s">
-        <v>108</v>
+      <c r="M14" s="33" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="90">
-      <c r="A15" s="36"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="43">
+      <c r="A15" s="35"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="41">
         <v>599760</v>
       </c>
-      <c r="E15" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="46" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="36">
+      <c r="E15" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="35">
         <v>56</v>
       </c>
-      <c r="I15" s="76"/>
-      <c r="J15" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="34">
+      <c r="I15" s="84"/>
+      <c r="J15" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K15" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="33">
         <f t="shared" si="0"/>
         <v>10710</v>
       </c>
-      <c r="M15" s="34" t="s">
-        <v>109</v>
+      <c r="M15" s="33" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="60">
-      <c r="A16" s="36"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="43">
+      <c r="A16" s="35"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="41">
         <v>299540</v>
       </c>
-      <c r="E16" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="36">
+      <c r="E16" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="35">
         <v>34</v>
       </c>
-      <c r="I16" s="76"/>
-      <c r="J16" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K16" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="34">
+      <c r="I16" s="84"/>
+      <c r="J16" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="33">
         <f t="shared" si="0"/>
         <v>8810</v>
       </c>
-      <c r="M16" s="34" t="s">
-        <v>110</v>
+      <c r="M16" s="33" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="75">
-      <c r="A17" s="36"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="43">
+      <c r="A17" s="35"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="41">
         <v>1205640</v>
       </c>
-      <c r="E17" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="36">
+      <c r="E17" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="35">
         <v>4</v>
       </c>
-      <c r="I17" s="76"/>
-      <c r="J17" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K17" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="L17" s="34">
+      <c r="I17" s="84"/>
+      <c r="J17" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" s="33">
         <f t="shared" si="0"/>
         <v>301410</v>
       </c>
-      <c r="M17" s="34" t="s">
-        <v>111</v>
+      <c r="M17" s="33" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="60">
-      <c r="A18" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="48" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I18" s="47"/>
-      <c r="J18" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K18" s="36"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
+      <c r="A18" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="35"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="47"/>
-      <c r="J19" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="36"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
+      <c r="A19" s="45"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" s="35"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="47"/>
-      <c r="J20" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
+      <c r="A20" s="45"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="45"/>
+      <c r="J20" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="35"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="47"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="49" t="s">
+      <c r="A21" s="45"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="45"/>
+      <c r="J21" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="35"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="48"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="45"/>
+      <c r="J22" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K22" s="35"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="48"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="45"/>
+      <c r="J23" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K23" s="35"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="48"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="45"/>
+      <c r="J24" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K24" s="35"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="48"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="45"/>
+      <c r="J25" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="35"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="48"/>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I26" s="45"/>
+      <c r="J26" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K26" s="35"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="48"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27" s="45"/>
+      <c r="J27" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K27" s="35"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="48"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I28" s="45"/>
+      <c r="J28" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K28" s="35"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="48"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="46" t="s">
+        <v>80</v>
+      </c>
+      <c r="I29" s="45"/>
+      <c r="J29" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="K29" s="35"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+    </row>
+    <row r="30" spans="1:13" ht="100.5" customHeight="1">
+      <c r="A30" s="49">
+        <v>112026</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="45"/>
+      <c r="D30" s="50">
+        <v>2285334</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="54">
+        <v>65000</v>
+      </c>
+      <c r="I30" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="J30" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="47"/>
-      <c r="J21" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K21" s="36"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="50"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I22" s="47"/>
-      <c r="J22" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="50"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="47"/>
-      <c r="J23" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="36"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="50"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I24" s="47"/>
-      <c r="J24" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K24" s="36"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="50"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="47"/>
-      <c r="J25" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K25" s="36"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34"/>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="50"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I26" s="47"/>
-      <c r="J26" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="36"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="50"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" s="47"/>
-      <c r="J27" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K27" s="36"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="50"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I28" s="47"/>
-      <c r="J28" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K28" s="36"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="50"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="I29" s="47"/>
-      <c r="J29" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="K29" s="36"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-    </row>
-    <row r="30" spans="1:13" ht="100.5" customHeight="1">
-      <c r="A30" s="51">
-        <v>112026</v>
-      </c>
-      <c r="B30" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="52">
-        <v>2285334</v>
-      </c>
-      <c r="E30" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="55" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="56">
-        <v>65000</v>
-      </c>
-      <c r="I30" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="J30" s="55" t="s">
-        <v>82</v>
-      </c>
-      <c r="K30" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="L30" s="38">
+      <c r="K30" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="L30" s="37">
         <f>D30/H30</f>
         <v>35.158984615384618</v>
       </c>
-      <c r="M30" s="34" t="s">
-        <v>113</v>
+      <c r="M30" s="33" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4093,8 +4478,8 @@
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="27" t="s">
-        <v>72</v>
+      <c r="A33" s="26" t="s">
+        <v>81</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -4584,125 +4969,125 @@
         <v>9</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="L1" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="M1" s="30" t="s">
-        <v>86</v>
+        <v>101</v>
+      </c>
+      <c r="L1" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="225">
-      <c r="A2" s="79">
+      <c r="A2" s="88">
         <v>104187</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="79">
+      <c r="B2" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="88">
         <v>4934228</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="O2" s="29"/>
+        <v>106</v>
+      </c>
+      <c r="I2" s="90" t="s">
+        <v>107</v>
+      </c>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="O2" s="28"/>
     </row>
     <row r="3" spans="1:15" ht="135">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="81"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
+        <v>34</v>
+      </c>
+      <c r="I3" s="90"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
     </row>
     <row r="4" spans="1:15" ht="240">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="81"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
+        <v>38</v>
+      </c>
+      <c r="I4" s="90"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
     </row>
     <row r="5" spans="1:15" ht="150">
       <c r="A5" s="2">
         <v>111777</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2">
         <v>716641</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L5" s="31">
+        <v>111</v>
+      </c>
+      <c r="L5" s="30">
         <f>D5/827</f>
         <v>866.5550181378477</v>
       </c>
-      <c r="M5" s="30" t="s">
-        <v>95</v>
+      <c r="M5" s="29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="225">
@@ -4710,844 +5095,844 @@
         <v>111777</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5">
         <v>716641</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L6" s="31">
+        <v>114</v>
+      </c>
+      <c r="L6" s="30">
         <f>D6/827</f>
         <v>866.5550181378477</v>
       </c>
-      <c r="M6" s="30" t="s">
-        <v>98</v>
+      <c r="M6" s="29" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="255">
       <c r="C7" s="3"/>
       <c r="D7" s="5"/>
       <c r="E7" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>99</v>
+        <v>26</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="K7" s="14"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
     </row>
     <row r="8" spans="1:15" ht="60">
       <c r="A8" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D8" s="6">
         <v>1348200</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2">
         <v>5000</v>
       </c>
-      <c r="I8" s="75" t="s">
-        <v>54</v>
+      <c r="I8" s="87" t="s">
+        <v>119</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="30">
+        <v>57</v>
+      </c>
+      <c r="L8" s="29">
         <f t="shared" ref="L8:L17" si="0">D8/H8</f>
         <v>269.64</v>
       </c>
-      <c r="M8" s="30" t="s">
-        <v>102</v>
+      <c r="M8" s="29" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="45">
       <c r="A9" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D9" s="6">
         <v>1624000</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="6">
         <v>50000</v>
       </c>
-      <c r="I9" s="75"/>
+      <c r="I9" s="87"/>
       <c r="J9" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="30">
+        <v>57</v>
+      </c>
+      <c r="L9" s="29">
         <f t="shared" si="0"/>
         <v>32.479999999999997</v>
       </c>
-      <c r="M9" s="30" t="s">
-        <v>103</v>
+      <c r="M9" s="29" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="60">
       <c r="A10" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D10" s="6">
         <v>753600</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2">
         <v>100</v>
       </c>
-      <c r="I10" s="75"/>
+      <c r="I10" s="87"/>
       <c r="J10" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="30">
+        <v>57</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="29">
         <f t="shared" si="0"/>
         <v>7536</v>
       </c>
-      <c r="M10" s="30" t="s">
-        <v>105</v>
+      <c r="M10" s="29" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="60">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D11" s="6">
         <v>1906800</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H11" s="2">
         <v>168</v>
       </c>
-      <c r="I11" s="75"/>
+      <c r="I11" s="87"/>
       <c r="J11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="30">
+        <v>57</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="29">
         <f t="shared" si="0"/>
         <v>11350</v>
       </c>
-      <c r="M11" s="30" t="s">
-        <v>106</v>
+      <c r="M11" s="29" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="90">
       <c r="A12" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D12" s="6">
         <v>682360</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="2">
         <v>56</v>
       </c>
-      <c r="I12" s="75"/>
+      <c r="I12" s="87"/>
       <c r="J12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="30">
+        <v>57</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L12" s="29">
         <f t="shared" si="0"/>
         <v>12185</v>
       </c>
-      <c r="M12" s="30" t="s">
-        <v>107</v>
+      <c r="M12" s="29" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="135">
       <c r="A13" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D13" s="6">
         <v>529200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="2">
         <v>56</v>
       </c>
-      <c r="I13" s="75"/>
+      <c r="I13" s="87"/>
       <c r="J13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="30">
+        <v>57</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" s="29">
         <f t="shared" si="0"/>
         <v>9450</v>
       </c>
-      <c r="M13" s="30" t="s">
-        <v>108</v>
+      <c r="M13" s="29" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="90">
       <c r="A14" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6">
         <v>1030400</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="2">
         <v>100</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="87"/>
       <c r="J14" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L14" s="30">
+        <v>57</v>
+      </c>
+      <c r="L14" s="29">
         <f t="shared" si="0"/>
         <v>10304</v>
       </c>
-      <c r="M14" s="30" t="s">
-        <v>108</v>
+      <c r="M14" s="29" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="90">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="11">
         <v>599760</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="10">
         <v>56</v>
       </c>
-      <c r="I15" s="75"/>
+      <c r="I15" s="87"/>
       <c r="J15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="30">
+        <v>57</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="29">
         <f t="shared" si="0"/>
         <v>10710</v>
       </c>
-      <c r="M15" s="30" t="s">
-        <v>109</v>
+      <c r="M15" s="29" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="60">
       <c r="A16" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="11">
         <v>299540</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>67</v>
+        <v>41</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="10">
         <v>34</v>
       </c>
-      <c r="I16" s="75"/>
+      <c r="I16" s="87"/>
       <c r="J16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="30">
+        <v>57</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L16" s="29">
         <f t="shared" si="0"/>
         <v>8810</v>
       </c>
-      <c r="M16" s="30" t="s">
-        <v>110</v>
+      <c r="M16" s="29" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="75">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="11">
         <v>1205640</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>76</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" s="10">
         <v>4</v>
       </c>
-      <c r="I17" s="75"/>
+      <c r="I17" s="87"/>
       <c r="J17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="L17" s="30">
+        <v>57</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" s="29">
         <f t="shared" si="0"/>
         <v>301410</v>
       </c>
-      <c r="M17" s="30" t="s">
-        <v>111</v>
+      <c r="M17" s="29" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="60">
       <c r="A18" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>71</v>
+        <v>132</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
     </row>
     <row r="19" spans="1:13" ht="60">
       <c r="A19" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>71</v>
+        <v>132</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
     </row>
     <row r="20" spans="1:13" ht="60">
       <c r="A20" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>71</v>
+        <v>132</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
     </row>
     <row r="21" spans="1:13" ht="60">
       <c r="A21" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>71</v>
+        <v>132</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
     </row>
     <row r="22" spans="1:13" ht="60">
-      <c r="A22" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>71</v>
+      <c r="A22" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
     </row>
     <row r="23" spans="1:13" ht="60">
-      <c r="A23" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>71</v>
+      <c r="A23" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
     </row>
     <row r="24" spans="1:13" ht="60">
-      <c r="A24" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>71</v>
+      <c r="A24" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
     </row>
     <row r="25" spans="1:13" ht="60">
-      <c r="A25" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>71</v>
+      <c r="A25" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L25" s="30"/>
-      <c r="M25" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
     </row>
     <row r="26" spans="1:13" ht="60">
-      <c r="A26" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>71</v>
+      <c r="A26" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
     </row>
     <row r="27" spans="1:13" ht="60">
-      <c r="A27" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>71</v>
+      <c r="A27" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
     </row>
     <row r="28" spans="1:13" ht="60">
-      <c r="A28" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="25" t="s">
+      <c r="A28" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>71</v>
+      <c r="C28" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
     </row>
     <row r="29" spans="1:13" ht="60">
-      <c r="A29" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="25" t="s">
+      <c r="A29" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="24" t="s">
-        <v>71</v>
+      <c r="F29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
+        <v>57</v>
+      </c>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
     </row>
     <row r="30" spans="1:13" ht="100.5" customHeight="1">
       <c r="A30" s="17">
         <v>112026</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="16">
         <v>2285334</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" s="20">
         <v>65000</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="L30" s="31">
+        <v>93</v>
+      </c>
+      <c r="L30" s="30">
         <f>D30/H30</f>
         <v>35.158984615384618</v>
       </c>
-      <c r="M30" s="30" t="s">
-        <v>113</v>
+      <c r="M30" s="29" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -5573,8 +5958,8 @@
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="27" t="s">
-        <v>72</v>
+      <c r="A33" s="26" t="s">
+        <v>81</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -6030,7 +6415,7 @@
     <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="30.75">
+    <row r="1" spans="1:13" ht="30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6062,778 +6447,778 @@
         <v>9</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="213">
-      <c r="A2" s="79">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="225">
+      <c r="A2" s="88">
         <v>104187</v>
       </c>
-      <c r="B2" s="79" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="79">
+      <c r="B2" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="88">
         <v>4934228</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I2" s="81" t="s">
-        <v>90</v>
-      </c>
-      <c r="L2" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="M2" s="29"/>
+        <v>106</v>
+      </c>
+      <c r="I2" s="90" t="s">
+        <v>107</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="M2" s="28"/>
     </row>
     <row r="3" spans="1:13" ht="135">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="81"/>
+        <v>34</v>
+      </c>
+      <c r="I3" s="90"/>
     </row>
     <row r="4" spans="1:13" ht="240">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="81"/>
+        <v>38</v>
+      </c>
+      <c r="I4" s="90"/>
     </row>
     <row r="5" spans="1:13" ht="120">
       <c r="A5" s="2">
         <v>111777</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2">
         <v>716641</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="121.5">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="120">
       <c r="C6" s="3"/>
       <c r="D6" s="5"/>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="255">
       <c r="C7" s="3"/>
       <c r="D7" s="5"/>
       <c r="E7" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="22" t="s">
-        <v>99</v>
+        <v>26</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="K7" s="14"/>
     </row>
-    <row r="8" spans="1:13" ht="121.5">
+    <row r="8" spans="1:13" ht="120">
       <c r="A8" s="2" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D8" s="6">
         <v>1348200</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2">
         <v>5000</v>
       </c>
-      <c r="I8" s="75" t="s">
-        <v>54</v>
+      <c r="I8" s="87" t="s">
+        <v>119</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45.75">
+        <v>57</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="45">
       <c r="B9" s="7"/>
       <c r="D9" s="6">
         <v>1624000</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="6">
         <v>50000</v>
       </c>
-      <c r="I9" s="75"/>
+      <c r="I9" s="87"/>
       <c r="J9" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="60.75">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="60">
       <c r="B10" s="7"/>
       <c r="D10" s="6">
         <v>753600</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2">
         <v>100</v>
       </c>
-      <c r="I10" s="75"/>
+      <c r="I10" s="87"/>
       <c r="J10" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="60.75">
+        <v>57</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="60">
       <c r="B11" s="7"/>
       <c r="D11" s="6">
         <v>1906800</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H11" s="2">
         <v>168</v>
       </c>
-      <c r="I11" s="75"/>
+      <c r="I11" s="87"/>
       <c r="J11" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" s="28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="91.5">
+        <v>57</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="90">
       <c r="B12" s="7"/>
       <c r="D12" s="6">
         <v>682360</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="2">
         <v>56</v>
       </c>
-      <c r="I12" s="75"/>
+      <c r="I12" s="87"/>
       <c r="J12" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="106.5">
+        <v>57</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="135">
       <c r="B13" s="7"/>
       <c r="D13" s="6">
         <v>529200</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="2">
         <v>56</v>
       </c>
-      <c r="I13" s="75"/>
+      <c r="I13" s="87"/>
       <c r="J13" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="28" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="91.5">
+        <v>57</v>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="90">
       <c r="B14" s="7"/>
       <c r="D14" s="6">
         <v>1030400</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="2">
         <v>100</v>
       </c>
-      <c r="I14" s="75"/>
+      <c r="I14" s="87"/>
       <c r="J14" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="91.5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="90">
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11">
         <v>599760</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>73</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="10">
         <v>56</v>
       </c>
-      <c r="I15" s="75"/>
+      <c r="I15" s="87"/>
       <c r="J15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="60.75">
+        <v>57</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="60">
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11">
         <v>299540</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>67</v>
+        <v>41</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>74</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="10">
         <v>34</v>
       </c>
-      <c r="I16" s="75"/>
+      <c r="I16" s="87"/>
       <c r="J16" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="76.5">
+        <v>57</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="75">
       <c r="B17" s="9"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11">
         <v>1205640</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>68</v>
+        <v>41</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>76</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" s="10">
         <v>4</v>
       </c>
-      <c r="I17" s="75"/>
+      <c r="I17" s="87"/>
       <c r="J17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K17" s="28" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="76.5" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>71</v>
+        <v>132</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I18" s="8"/>
       <c r="J18" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" s="83" t="s">
-        <v>118</v>
+        <v>57</v>
+      </c>
+      <c r="L18" s="92" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="183" customHeight="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="24" t="s">
-        <v>71</v>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I19" s="8"/>
       <c r="J19" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K19" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="L19" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K19" s="91" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19" s="92"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="8"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="24" t="s">
-        <v>71</v>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I20" s="8"/>
       <c r="J20" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K20" s="82"/>
-      <c r="L20" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K20" s="91"/>
+      <c r="L20" s="92"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="8"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="24" t="s">
-        <v>71</v>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I21" s="8"/>
       <c r="J21" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K21" s="82"/>
-      <c r="L21" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K21" s="91"/>
+      <c r="L21" s="92"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="26"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>71</v>
+      <c r="A22" s="25"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I22" s="8"/>
       <c r="J22" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" s="82"/>
-      <c r="L22" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K22" s="91"/>
+      <c r="L22" s="92"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="26"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>71</v>
+      <c r="A23" s="25"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I23" s="8"/>
       <c r="J23" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="82"/>
-      <c r="L23" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K23" s="91"/>
+      <c r="L23" s="92"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="26"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>71</v>
+      <c r="A24" s="25"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I24" s="8"/>
       <c r="J24" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K24" s="82"/>
-      <c r="L24" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K24" s="91"/>
+      <c r="L24" s="92"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="26"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>71</v>
+      <c r="A25" s="25"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K25" s="82"/>
-      <c r="L25" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K25" s="91"/>
+      <c r="L25" s="92"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="26"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>71</v>
+      <c r="A26" s="25"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" s="82"/>
-      <c r="L26" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K26" s="91"/>
+      <c r="L26" s="92"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="26"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="24" t="s">
-        <v>71</v>
+      <c r="A27" s="25"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K27" s="82"/>
-      <c r="L27" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K27" s="91"/>
+      <c r="L27" s="92"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="26"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="24" t="s">
-        <v>71</v>
+      <c r="A28" s="25"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K28" s="82"/>
-      <c r="L28" s="83"/>
+        <v>57</v>
+      </c>
+      <c r="K28" s="91"/>
+      <c r="L28" s="92"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="26"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E29" s="25" t="s">
+      <c r="A29" s="25"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="24" t="s">
-        <v>71</v>
+      <c r="F29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>80</v>
       </c>
       <c r="I29" s="8"/>
       <c r="J29" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="K29" s="82"/>
+        <v>57</v>
+      </c>
+      <c r="K29" s="91"/>
     </row>
     <row r="30" spans="1:12" ht="100.5" customHeight="1">
       <c r="A30" s="17">
         <v>112026</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="16">
         <v>2285334</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G30" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" s="20">
         <v>65000</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="L30" s="28" t="s">
-        <v>119</v>
+        <v>93</v>
+      </c>
+      <c r="L30" s="27" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -7304,179 +7689,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>120</v>
+    <row r="2" spans="1:2" ht="45">
+      <c r="A2" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="77" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="84" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="84" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="60" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="84" t="s">
-        <v>123</v>
-      </c>
-      <c r="B5" s="60" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="84" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="60" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="60" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="84" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="84" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="85" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="84" t="s">
-        <v>133</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="84" t="s">
-        <v>135</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>136</v>
+      <c r="A3" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="77" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="45">
+      <c r="A4" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="77" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="71" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="77" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="90">
+      <c r="A6" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="77" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45">
+      <c r="A7" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="77" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45">
+      <c r="A9" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" s="71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="72" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45">
+      <c r="A12" s="71" t="s">
+        <v>151</v>
+      </c>
+      <c r="B12" s="77" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="72" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="84" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="85" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="84" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="85" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="85" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="84" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="84" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="85" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="84" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="85" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="B20" s="85" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="84" t="s">
+      <c r="A14" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="B14" s="72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30">
+      <c r="A15" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="B15" s="72" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30">
+      <c r="A16" s="71" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="72" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30">
+      <c r="A17" s="71" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30">
+      <c r="A18" s="71" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="75">
+      <c r="A19" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="72" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30">
+      <c r="A20" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="72" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45">
+      <c r="A21" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="86" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="84" t="s">
-        <v>148</v>
-      </c>
-      <c r="B22" s="85" t="s">
-        <v>149</v>
+      <c r="B21" s="73" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="72" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -7548,15 +7933,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -7811,14 +8187,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87DAB1ED-73B6-46CD-978D-DDC5D0F3F477}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7AE853E-4F37-4A3C-B15C-49DE17FB657C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFBEADC0-4F19-45ED-914F-1FFE20B7C773}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFBEADC0-4F19-45ED-914F-1FFE20B7C773}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7AE853E-4F37-4A3C-B15C-49DE17FB657C}"/>
 </file>
--- a/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Myanmar - Energy Projects.xlsx
@@ -605,10 +605,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -715,8 +715,9 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={DFF87492-011A-4DFF-B2A2-0767EFA86F14}</author>
+    <author>CO validation update</author>
+    <author>tc={079A32D1-D600-4A60-B4CE-F2D4598DC6F2}</author>
     <author>Folashade Jaiyeola</author>
-    <author>tc={079A32D1-D600-4A60-B4CE-F2D4598DC6F2}</author>
     <author>tc={32BF67D8-AF94-4243-BB0C-9121426D1E0C}</author>
     <author>tc={2D8B2591-10A3-4BD9-800A-1F7644AFF05C}</author>
     <author>tc={A0D25A78-FA1F-4143-B02D-7892CF711E91}</author>
@@ -732,11 +733,14 @@
     @Stefano Pistolese  this is project is now cancelled in accordance's with GEF's directives</t>
       </text>
     </comment>
+    <comment ref="K2" authorId="1" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
     <comment ref="L2" authorId="1" shapeId="0">
       <text>
-        <t>Folashade Jaiyeola:
-Former: 2.89
-Deleted because project has been cancelled</t>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
       </text>
     </comment>
     <comment ref="B5" authorId="2" shapeId="0">
@@ -749,14 +753,24 @@
     @Stefano Pistolese  project is now operationally closed</t>
       </text>
     </comment>
-    <comment ref="B9" authorId="1" shapeId="0">
+    <comment ref="K8" authorId="1" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="1" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="3" shapeId="0">
       <text>
         <t xml:space="preserve">Folashade Jaiyeola:
 We should not include this project as it is not fully approved
 </t>
       </text>
     </comment>
-    <comment ref="M9" authorId="3" shapeId="0">
+    <comment ref="M9" authorId="4" shapeId="0">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -764,14 +778,14 @@
     @Stefano Pistolese the CO is no longer pursuing this partnership. We can remove it from here. Noted that all your questions are related to this particular project. </t>
       </text>
     </comment>
-    <comment ref="B19" authorId="1" shapeId="0">
+    <comment ref="B19" authorId="3" shapeId="0">
       <text>
         <t xml:space="preserve">Folashade Jaiyeola:
 We should not include this project as it is still in approval stage
 </t>
       </text>
     </comment>
-    <comment ref="B31" authorId="4" shapeId="0">
+    <comment ref="B31" authorId="5" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -781,7 +795,7 @@
     @Stefano Pistolese  project is now operationally closed</t>
       </text>
     </comment>
-    <comment ref="B32" authorId="5" shapeId="0">
+    <comment ref="B32" authorId="6" shapeId="0">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -789,6 +803,16 @@
 There is a task anchored to this comment that cannot be viewed in your client.
 Comment:
     @Stefano Pistolese new</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="1" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="1" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
       </text>
     </comment>
   </commentList>
@@ -1290,17 +1314,17 @@
           <t>MW</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="K2" s="94" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="L2" s="94" t="n"/>
-      <c r="M2" s="94" t="inlineStr">
-        <is>
-          <t>Suspension of project likely to be extended
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Suspension of project likely to be extended
 246,094 tCO2 over the 12-yr lifetime of small hydro and solar mini-grids (20,508 tCO2 per year), and corresponding energy production of 25,341 MWh per year -&gt; 2.89 MW added
-[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+</t>
         </is>
       </c>
       <c r="P2" s="62" t="n"/>
@@ -1595,15 +1619,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K8" s="96" t="n">
+      <c r="K8" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="97" t="n"/>
-      <c r="M8" s="98" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="L8" s="98" t="n"/>
+      <c r="M8" s="96" t="n"/>
       <c r="N8" s="95" t="n"/>
       <c r="O8" s="95" t="n"/>
       <c r="P8" s="99" t="n"/>
@@ -2841,15 +2861,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K35" s="74" t="n">
+      <c r="K35" s="104" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="104" t="n"/>
-      <c r="M35" s="104" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M35" s="74" t="n"/>
       <c r="N35" s="27" t="n"/>
       <c r="O35" s="95" t="n"/>
       <c r="P35" s="95" t="n"/>
@@ -3405,7 +3421,7 @@
       <c r="M71" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="10">
     <dataValidation sqref="Q2:Q30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -3432,12 +3448,6 @@
     </dataValidation>
     <dataValidation sqref="S2:S30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
@@ -3704,9 +3714,8 @@
       </c>
       <c r="J5" s="35" t="n"/>
       <c r="K5" s="35" t="n"/>
-      <c r="L5" s="37">
-        <f>D5/827</f>
-        <v/>
+      <c r="L5" s="37" t="n">
+        <v>866.5550181378477</v>
       </c>
       <c r="M5" s="33" t="inlineStr">
         <is>
@@ -3758,9 +3767,8 @@
       </c>
       <c r="J6" s="35" t="n"/>
       <c r="K6" s="35" t="n"/>
-      <c r="L6" s="37">
-        <f>D6/827</f>
-        <v/>
+      <c r="L6" s="37" t="n">
+        <v>866.5550181378477</v>
       </c>
       <c r="M6" s="33" t="inlineStr">
         <is>
@@ -3851,9 +3859,8 @@
         </is>
       </c>
       <c r="K8" s="35" t="n"/>
-      <c r="L8" s="33">
-        <f>D8/H8</f>
-        <v/>
+      <c r="L8" s="33" t="n">
+        <v>269.64</v>
       </c>
       <c r="M8" s="33" t="inlineStr">
         <is>
@@ -3893,9 +3900,8 @@
         </is>
       </c>
       <c r="K9" s="35" t="n"/>
-      <c r="L9" s="33">
-        <f>D9/H9</f>
-        <v/>
+      <c r="L9" s="33" t="n">
+        <v>32.48</v>
       </c>
       <c r="M9" s="33" t="inlineStr">
         <is>
@@ -3939,9 +3945,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L10" s="33">
-        <f>D10/H10</f>
-        <v/>
+      <c r="L10" s="33" t="n">
+        <v>7536</v>
       </c>
       <c r="M10" s="33" t="inlineStr">
         <is>
@@ -3981,9 +3986,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L11" s="33">
-        <f>D11/H11</f>
-        <v/>
+      <c r="L11" s="33" t="n">
+        <v>11350</v>
       </c>
       <c r="M11" s="33" t="inlineStr">
         <is>
@@ -4027,9 +4031,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L12" s="33">
-        <f>D12/H12</f>
-        <v/>
+      <c r="L12" s="33" t="n">
+        <v>12185</v>
       </c>
       <c r="M12" s="33" t="inlineStr">
         <is>
@@ -4073,9 +4076,8 @@
           <t>Estimate # of beneficiaries / system</t>
         </is>
       </c>
-      <c r="L13" s="33">
-        <f>D13/H13</f>
-        <v/>
+      <c r="L13" s="33" t="n">
+        <v>9450</v>
       </c>
       <c r="M13" s="33" t="inlineStr">
         <is>
@@ -4115,9 +4117,8 @@
         </is>
       </c>
       <c r="K14" s="35" t="n"/>
-      <c r="L14" s="33">
-        <f>D14/H14</f>
-        <v/>
+      <c r="L14" s="33" t="n">
+        <v>10304</v>
       </c>
       <c r="M14" s="33" t="inlineStr">
         <is>
@@ -4162,9 +4163,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L15" s="33">
-        <f>D15/H15</f>
-        <v/>
+      <c r="L15" s="33" t="n">
+        <v>10710</v>
       </c>
       <c r="M15" s="33" t="inlineStr">
         <is>
@@ -4208,9 +4208,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L16" s="33">
-        <f>D16/H16</f>
-        <v/>
+      <c r="L16" s="33" t="n">
+        <v>8810</v>
       </c>
       <c r="M16" s="33" t="inlineStr">
         <is>
@@ -4254,9 +4253,8 @@
           <t>Estimate # of beneficiaries / system</t>
         </is>
       </c>
-      <c r="L17" s="33">
-        <f>D17/H17</f>
-        <v/>
+      <c r="L17" s="33" t="n">
+        <v>301410</v>
       </c>
       <c r="M17" s="33" t="inlineStr">
         <is>
@@ -4834,9 +4832,8 @@
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="L30" s="37">
-        <f>D30/H30</f>
-        <v/>
+      <c r="L30" s="37" t="n">
+        <v>35.15898461538462</v>
       </c>
       <c r="M30" s="33" t="inlineStr">
         <is>
@@ -5527,9 +5524,8 @@
           <t>GRSP's budget for 2022 was $716,641.</t>
         </is>
       </c>
-      <c r="L5" s="30">
-        <f>D5/827</f>
-        <v/>
+      <c r="L5" s="30" t="n">
+        <v>866.5550181378477</v>
       </c>
       <c r="M5" s="29" t="inlineStr">
         <is>
@@ -5579,9 +5575,8 @@
           <t xml:space="preserve">GRSP's budget for 2022 was $716,641. The project was concluded in 2022. </t>
         </is>
       </c>
-      <c r="L6" s="30">
-        <f>D6/827</f>
-        <v/>
+      <c r="L6" s="30" t="n">
+        <v>866.5550181378477</v>
       </c>
       <c r="M6" s="29" t="inlineStr">
         <is>
@@ -5667,9 +5662,8 @@
           <t>in search of donor</t>
         </is>
       </c>
-      <c r="L8" s="29">
-        <f>D8/H8</f>
-        <v/>
+      <c r="L8" s="29" t="n">
+        <v>269.64</v>
       </c>
       <c r="M8" s="29" t="inlineStr">
         <is>
@@ -5715,9 +5709,8 @@
           <t>in search of donor</t>
         </is>
       </c>
-      <c r="L9" s="29">
-        <f>D9/H9</f>
-        <v/>
+      <c r="L9" s="29" t="n">
+        <v>32.48</v>
       </c>
       <c r="M9" s="29" t="inlineStr">
         <is>
@@ -5768,9 +5761,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L10" s="29">
-        <f>D10/H10</f>
-        <v/>
+      <c r="L10" s="29" t="n">
+        <v>7536</v>
       </c>
       <c r="M10" s="29" t="inlineStr">
         <is>
@@ -5816,9 +5808,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L11" s="29">
-        <f>D11/H11</f>
-        <v/>
+      <c r="L11" s="29" t="n">
+        <v>11350</v>
       </c>
       <c r="M11" s="29" t="inlineStr">
         <is>
@@ -5869,9 +5860,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L12" s="29">
-        <f>D12/H12</f>
-        <v/>
+      <c r="L12" s="29" t="n">
+        <v>12185</v>
       </c>
       <c r="M12" s="29" t="inlineStr">
         <is>
@@ -5922,9 +5912,8 @@
           <t>Estimate # of beneficiaries / system</t>
         </is>
       </c>
-      <c r="L13" s="29">
-        <f>D13/H13</f>
-        <v/>
+      <c r="L13" s="29" t="n">
+        <v>9450</v>
       </c>
       <c r="M13" s="29" t="inlineStr">
         <is>
@@ -5970,9 +5959,8 @@
           <t>in search of donor</t>
         </is>
       </c>
-      <c r="L14" s="29">
-        <f>D14/H14</f>
-        <v/>
+      <c r="L14" s="29" t="n">
+        <v>10304</v>
       </c>
       <c r="M14" s="29" t="inlineStr">
         <is>
@@ -6025,9 +6013,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L15" s="29">
-        <f>D15/H15</f>
-        <v/>
+      <c r="L15" s="29" t="n">
+        <v>10710</v>
       </c>
       <c r="M15" s="29" t="inlineStr">
         <is>
@@ -6079,9 +6066,8 @@
           <t>Estimate # of beneficiaries / village</t>
         </is>
       </c>
-      <c r="L16" s="29">
-        <f>D16/H16</f>
-        <v/>
+      <c r="L16" s="29" t="n">
+        <v>8810</v>
       </c>
       <c r="M16" s="29" t="inlineStr">
         <is>
@@ -6133,9 +6119,8 @@
           <t>Estimate # of beneficiaries / system</t>
         </is>
       </c>
-      <c r="L17" s="29">
-        <f>D17/H17</f>
-        <v/>
+      <c r="L17" s="29" t="n">
+        <v>301410</v>
       </c>
       <c r="M17" s="29" t="inlineStr">
         <is>
@@ -6789,9 +6774,8 @@
           <t>Ongoing</t>
         </is>
       </c>
-      <c r="L30" s="30">
-        <f>D30/H30</f>
-        <v/>
+      <c r="L30" s="30" t="n">
+        <v>35.15898461538462</v>
       </c>
       <c r="M30" s="29" t="inlineStr">
         <is>
